--- a/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -711,25 +711,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>32286600</v>
+        <v>32835500</v>
       </c>
       <c r="E8" s="3">
-        <v>15275000</v>
+        <v>15534700</v>
       </c>
       <c r="F8" s="3">
-        <v>12635300</v>
+        <v>12850100</v>
       </c>
       <c r="G8" s="3">
-        <v>15803600</v>
+        <v>16072300</v>
       </c>
       <c r="H8" s="3">
-        <v>20106800</v>
+        <v>20448700</v>
       </c>
       <c r="I8" s="3">
-        <v>19621600</v>
+        <v>19955200</v>
       </c>
       <c r="J8" s="3">
-        <v>18840600</v>
+        <v>19161000</v>
       </c>
       <c r="K8" s="3">
         <v>19417200</v>
@@ -905,25 +905,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-326700</v>
+        <v>-332300</v>
       </c>
       <c r="E15" s="3">
-        <v>-374000</v>
+        <v>-380300</v>
       </c>
       <c r="F15" s="3">
-        <v>-412800</v>
+        <v>-419800</v>
       </c>
       <c r="G15" s="3">
-        <v>-555100</v>
+        <v>-564600</v>
       </c>
       <c r="H15" s="3">
-        <v>-449000</v>
+        <v>-456700</v>
       </c>
       <c r="I15" s="3">
-        <v>-640500</v>
+        <v>-651400</v>
       </c>
       <c r="J15" s="3">
-        <v>-466500</v>
+        <v>-474400</v>
       </c>
       <c r="K15" s="3">
         <v>-956200</v>
@@ -946,25 +946,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21717200</v>
+        <v>22086400</v>
       </c>
       <c r="E17" s="3">
-        <v>5501400</v>
+        <v>5595000</v>
       </c>
       <c r="F17" s="3">
-        <v>3106200</v>
+        <v>3159100</v>
       </c>
       <c r="G17" s="3">
-        <v>8485400</v>
+        <v>8629700</v>
       </c>
       <c r="H17" s="3">
-        <v>11343200</v>
+        <v>11536100</v>
       </c>
       <c r="I17" s="3">
-        <v>10676100</v>
+        <v>10857700</v>
       </c>
       <c r="J17" s="3">
-        <v>9991600</v>
+        <v>10161500</v>
       </c>
       <c r="K17" s="3">
         <v>10881700</v>
@@ -976,25 +976,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10569400</v>
+        <v>10749100</v>
       </c>
       <c r="E18" s="3">
-        <v>9773600</v>
+        <v>9939700</v>
       </c>
       <c r="F18" s="3">
-        <v>9529000</v>
+        <v>9691000</v>
       </c>
       <c r="G18" s="3">
-        <v>7318200</v>
+        <v>7442600</v>
       </c>
       <c r="H18" s="3">
-        <v>8763600</v>
+        <v>8912600</v>
       </c>
       <c r="I18" s="3">
-        <v>8945400</v>
+        <v>9097500</v>
       </c>
       <c r="J18" s="3">
-        <v>8849000</v>
+        <v>8999500</v>
       </c>
       <c r="K18" s="3">
         <v>8535500</v>
@@ -1020,25 +1020,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4050900</v>
+        <v>-4119700</v>
       </c>
       <c r="E20" s="3">
-        <v>-3252500</v>
+        <v>-3307800</v>
       </c>
       <c r="F20" s="3">
-        <v>-3747400</v>
+        <v>-3811100</v>
       </c>
       <c r="G20" s="3">
-        <v>-3749400</v>
+        <v>-3813100</v>
       </c>
       <c r="H20" s="3">
-        <v>-2992400</v>
+        <v>-3043300</v>
       </c>
       <c r="I20" s="3">
-        <v>-2543400</v>
+        <v>-2586600</v>
       </c>
       <c r="J20" s="3">
-        <v>-2875300</v>
+        <v>-2924200</v>
       </c>
       <c r="K20" s="3">
         <v>-3233700</v>
@@ -1050,25 +1050,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7118900</v>
+        <v>7240400</v>
       </c>
       <c r="E21" s="3">
-        <v>7176800</v>
+        <v>7299300</v>
       </c>
       <c r="F21" s="3">
-        <v>6488700</v>
+        <v>6599500</v>
       </c>
       <c r="G21" s="3">
-        <v>4473700</v>
+        <v>4550400</v>
       </c>
       <c r="H21" s="3">
-        <v>6337800</v>
+        <v>6446000</v>
       </c>
       <c r="I21" s="3">
-        <v>7182000</v>
+        <v>7304600</v>
       </c>
       <c r="J21" s="3">
-        <v>6606000</v>
+        <v>6718800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1110,25 +1110,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6518500</v>
+        <v>6629400</v>
       </c>
       <c r="E23" s="3">
-        <v>6521100</v>
+        <v>6632000</v>
       </c>
       <c r="F23" s="3">
-        <v>5781600</v>
+        <v>5879900</v>
       </c>
       <c r="G23" s="3">
-        <v>3568900</v>
+        <v>3629500</v>
       </c>
       <c r="H23" s="3">
-        <v>5771200</v>
+        <v>5869400</v>
       </c>
       <c r="I23" s="3">
-        <v>6402100</v>
+        <v>6510900</v>
       </c>
       <c r="J23" s="3">
-        <v>5973800</v>
+        <v>6075300</v>
       </c>
       <c r="K23" s="3">
         <v>5301800</v>
@@ -1140,25 +1140,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1908000</v>
+        <v>1940400</v>
       </c>
       <c r="E24" s="3">
-        <v>1902200</v>
+        <v>1934500</v>
       </c>
       <c r="F24" s="3">
-        <v>1783100</v>
+        <v>1813400</v>
       </c>
       <c r="G24" s="3">
-        <v>1190500</v>
+        <v>1210700</v>
       </c>
       <c r="H24" s="3">
-        <v>1688000</v>
+        <v>1716700</v>
       </c>
       <c r="I24" s="3">
-        <v>1801200</v>
+        <v>1831900</v>
       </c>
       <c r="J24" s="3">
-        <v>1859500</v>
+        <v>1891100</v>
       </c>
       <c r="K24" s="3">
         <v>1593500</v>
@@ -1200,25 +1200,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4610500</v>
+        <v>4688900</v>
       </c>
       <c r="E26" s="3">
-        <v>4618900</v>
+        <v>4697500</v>
       </c>
       <c r="F26" s="3">
-        <v>3998500</v>
+        <v>4066400</v>
       </c>
       <c r="G26" s="3">
-        <v>2378400</v>
+        <v>2418800</v>
       </c>
       <c r="H26" s="3">
-        <v>4083200</v>
+        <v>4152600</v>
       </c>
       <c r="I26" s="3">
-        <v>4600800</v>
+        <v>4679000</v>
       </c>
       <c r="J26" s="3">
-        <v>4114300</v>
+        <v>4184200</v>
       </c>
       <c r="K26" s="3">
         <v>3708300</v>
@@ -1230,25 +1230,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4592400</v>
+        <v>4670500</v>
       </c>
       <c r="E27" s="3">
-        <v>4618300</v>
+        <v>4696800</v>
       </c>
       <c r="F27" s="3">
-        <v>3997800</v>
+        <v>4065800</v>
       </c>
       <c r="G27" s="3">
-        <v>2377700</v>
+        <v>2418200</v>
       </c>
       <c r="H27" s="3">
-        <v>4073500</v>
+        <v>4142800</v>
       </c>
       <c r="I27" s="3">
-        <v>4590500</v>
+        <v>4668500</v>
       </c>
       <c r="J27" s="3">
-        <v>4104600</v>
+        <v>4174400</v>
       </c>
       <c r="K27" s="3">
         <v>3701100</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-12300</v>
+        <v>-12500</v>
       </c>
       <c r="F29" s="3">
-        <v>-11000</v>
+        <v>-11200</v>
       </c>
       <c r="G29" s="3">
-        <v>-63400</v>
+        <v>-64500</v>
       </c>
       <c r="H29" s="3">
-        <v>-221900</v>
+        <v>-225700</v>
       </c>
       <c r="I29" s="3">
-        <v>-449700</v>
+        <v>-457300</v>
       </c>
       <c r="J29" s="3">
-        <v>40100</v>
+        <v>40800</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1380,25 +1380,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4050900</v>
+        <v>4119700</v>
       </c>
       <c r="E32" s="3">
-        <v>3252500</v>
+        <v>3307800</v>
       </c>
       <c r="F32" s="3">
-        <v>3747400</v>
+        <v>3811100</v>
       </c>
       <c r="G32" s="3">
-        <v>3749400</v>
+        <v>3813100</v>
       </c>
       <c r="H32" s="3">
-        <v>2992400</v>
+        <v>3043300</v>
       </c>
       <c r="I32" s="3">
-        <v>2543400</v>
+        <v>2586600</v>
       </c>
       <c r="J32" s="3">
-        <v>2875300</v>
+        <v>2924200</v>
       </c>
       <c r="K32" s="3">
         <v>3233700</v>
@@ -1410,25 +1410,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4592400</v>
+        <v>4670500</v>
       </c>
       <c r="E33" s="3">
-        <v>4606000</v>
+        <v>4684300</v>
       </c>
       <c r="F33" s="3">
-        <v>3986800</v>
+        <v>4054600</v>
       </c>
       <c r="G33" s="3">
-        <v>2314300</v>
+        <v>2353700</v>
       </c>
       <c r="H33" s="3">
-        <v>3851600</v>
+        <v>3917100</v>
       </c>
       <c r="I33" s="3">
-        <v>4140800</v>
+        <v>4211200</v>
       </c>
       <c r="J33" s="3">
-        <v>4144700</v>
+        <v>4215100</v>
       </c>
       <c r="K33" s="3">
         <v>3701100</v>
@@ -1470,25 +1470,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4592400</v>
+        <v>4670500</v>
       </c>
       <c r="E35" s="3">
-        <v>4606000</v>
+        <v>4684300</v>
       </c>
       <c r="F35" s="3">
-        <v>3986800</v>
+        <v>4054600</v>
       </c>
       <c r="G35" s="3">
-        <v>2314300</v>
+        <v>2353700</v>
       </c>
       <c r="H35" s="3">
-        <v>3851600</v>
+        <v>3917100</v>
       </c>
       <c r="I35" s="3">
-        <v>4140800</v>
+        <v>4211200</v>
       </c>
       <c r="J35" s="3">
-        <v>4144700</v>
+        <v>4215100</v>
       </c>
       <c r="K35" s="3">
         <v>3701100</v>
@@ -1563,25 +1563,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>98337500</v>
+        <v>100009000</v>
       </c>
       <c r="E41" s="3">
-        <v>105329000</v>
+        <v>107120000</v>
       </c>
       <c r="F41" s="3">
-        <v>95270800</v>
+        <v>96890500</v>
       </c>
       <c r="G41" s="3">
-        <v>55561800</v>
+        <v>56506400</v>
       </c>
       <c r="H41" s="3">
-        <v>44142200</v>
+        <v>44892700</v>
       </c>
       <c r="I41" s="3">
-        <v>97799200</v>
+        <v>99462000</v>
       </c>
       <c r="J41" s="3">
-        <v>39677300</v>
+        <v>40351800</v>
       </c>
       <c r="K41" s="3">
         <v>38753400</v>
@@ -1593,25 +1593,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>89078300</v>
+        <v>90592800</v>
       </c>
       <c r="E42" s="3">
-        <v>99707200</v>
+        <v>101402000</v>
       </c>
       <c r="F42" s="3">
-        <v>71274200</v>
+        <v>72485900</v>
       </c>
       <c r="G42" s="3">
-        <v>152792000</v>
+        <v>155390000</v>
       </c>
       <c r="H42" s="3">
-        <v>132067000</v>
+        <v>134312000</v>
       </c>
       <c r="I42" s="3">
-        <v>94179900</v>
+        <v>95781100</v>
       </c>
       <c r="J42" s="3">
-        <v>88443000</v>
+        <v>89946600</v>
       </c>
       <c r="K42" s="3">
         <v>109372000</v>
@@ -1743,25 +1743,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1519800</v>
+        <v>1545600</v>
       </c>
       <c r="E47" s="3">
-        <v>1411100</v>
+        <v>1435100</v>
       </c>
       <c r="F47" s="3">
-        <v>1275900</v>
+        <v>1297600</v>
       </c>
       <c r="G47" s="3">
-        <v>1400100</v>
+        <v>1423900</v>
       </c>
       <c r="H47" s="3">
-        <v>1913200</v>
+        <v>1945700</v>
       </c>
       <c r="I47" s="3">
-        <v>1651800</v>
+        <v>1679900</v>
       </c>
       <c r="J47" s="3">
-        <v>1454500</v>
+        <v>1479200</v>
       </c>
       <c r="K47" s="3">
         <v>2769500</v>
@@ -1773,25 +1773,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1328300</v>
+        <v>1350900</v>
       </c>
       <c r="E48" s="3">
-        <v>1572900</v>
+        <v>1599600</v>
       </c>
       <c r="F48" s="3">
-        <v>1768900</v>
+        <v>1799000</v>
       </c>
       <c r="G48" s="3">
-        <v>1949400</v>
+        <v>1982600</v>
       </c>
       <c r="H48" s="3">
-        <v>1244800</v>
+        <v>1266000</v>
       </c>
       <c r="I48" s="3">
-        <v>1186000</v>
+        <v>1206100</v>
       </c>
       <c r="J48" s="3">
-        <v>1271400</v>
+        <v>1293000</v>
       </c>
       <c r="K48" s="3">
         <v>1429500</v>
@@ -1803,25 +1803,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2625500</v>
+        <v>2670200</v>
       </c>
       <c r="E49" s="3">
-        <v>2508400</v>
+        <v>2551100</v>
       </c>
       <c r="F49" s="3">
-        <v>2668200</v>
+        <v>2713600</v>
       </c>
       <c r="G49" s="3">
-        <v>2833200</v>
+        <v>2881400</v>
       </c>
       <c r="H49" s="3">
-        <v>3145100</v>
+        <v>3198500</v>
       </c>
       <c r="I49" s="3">
-        <v>6379400</v>
+        <v>6487900</v>
       </c>
       <c r="J49" s="3">
-        <v>4509600</v>
+        <v>4586300</v>
       </c>
       <c r="K49" s="3">
         <v>4973800</v>
@@ -1893,25 +1893,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2158400</v>
+        <v>2195100</v>
       </c>
       <c r="E52" s="3">
-        <v>2189400</v>
+        <v>2226700</v>
       </c>
       <c r="F52" s="3">
-        <v>1513300</v>
+        <v>1539100</v>
       </c>
       <c r="G52" s="3">
-        <v>1374200</v>
+        <v>1397600</v>
       </c>
       <c r="H52" s="3">
-        <v>2062000</v>
+        <v>2097000</v>
       </c>
       <c r="I52" s="3">
-        <v>29159600</v>
+        <v>29655400</v>
       </c>
       <c r="J52" s="3">
-        <v>5593300</v>
+        <v>5688400</v>
       </c>
       <c r="K52" s="3">
         <v>403900</v>
@@ -1953,25 +1953,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>715336000</v>
+        <v>727498000</v>
       </c>
       <c r="E54" s="3">
-        <v>702467000</v>
+        <v>714410000</v>
       </c>
       <c r="F54" s="3">
-        <v>633321000</v>
+        <v>644088000</v>
       </c>
       <c r="G54" s="3">
-        <v>674359000</v>
+        <v>685824000</v>
       </c>
       <c r="H54" s="3">
-        <v>634796000</v>
+        <v>645588000</v>
       </c>
       <c r="I54" s="3">
-        <v>610239000</v>
+        <v>620614000</v>
       </c>
       <c r="J54" s="3">
-        <v>580570000</v>
+        <v>590441000</v>
       </c>
       <c r="K54" s="3">
         <v>593110000</v>
@@ -2011,25 +2011,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9734100</v>
+        <v>9899600</v>
       </c>
       <c r="E57" s="3">
-        <v>6363200</v>
+        <v>6471400</v>
       </c>
       <c r="F57" s="3">
-        <v>5594600</v>
+        <v>5689700</v>
       </c>
       <c r="G57" s="3">
-        <v>5905800</v>
+        <v>6006200</v>
       </c>
       <c r="H57" s="3">
-        <v>5155300</v>
+        <v>5242900</v>
       </c>
       <c r="I57" s="3">
-        <v>4460400</v>
+        <v>4536300</v>
       </c>
       <c r="J57" s="3">
-        <v>5402400</v>
+        <v>5494300</v>
       </c>
       <c r="K57" s="3">
         <v>1052200</v>
@@ -2071,25 +2071,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>197300</v>
+        <v>200700</v>
       </c>
       <c r="E59" s="3">
-        <v>536400</v>
+        <v>545500</v>
       </c>
       <c r="F59" s="3">
-        <v>271100</v>
+        <v>275700</v>
       </c>
       <c r="G59" s="3">
-        <v>225800</v>
+        <v>229600</v>
       </c>
       <c r="H59" s="3">
-        <v>168200</v>
+        <v>171100</v>
       </c>
       <c r="I59" s="3">
-        <v>194100</v>
+        <v>197400</v>
       </c>
       <c r="J59" s="3">
-        <v>155900</v>
+        <v>158600</v>
       </c>
       <c r="K59" s="3">
         <v>2063500</v>
@@ -2131,25 +2131,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>75061100</v>
+        <v>76337200</v>
       </c>
       <c r="E61" s="3">
-        <v>60645900</v>
+        <v>61677000</v>
       </c>
       <c r="F61" s="3">
-        <v>65381900</v>
+        <v>66493500</v>
       </c>
       <c r="G61" s="3">
-        <v>77425200</v>
+        <v>78741500</v>
       </c>
       <c r="H61" s="3">
-        <v>83910100</v>
+        <v>85336700</v>
       </c>
       <c r="I61" s="3">
-        <v>78402800</v>
+        <v>79735800</v>
       </c>
       <c r="J61" s="3">
-        <v>69858500</v>
+        <v>71046200</v>
       </c>
       <c r="K61" s="3">
         <v>74270500</v>
@@ -2161,25 +2161,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1532100</v>
+        <v>1558100</v>
       </c>
       <c r="E62" s="3">
-        <v>1620100</v>
+        <v>1647600</v>
       </c>
       <c r="F62" s="3">
-        <v>1867200</v>
+        <v>1899000</v>
       </c>
       <c r="G62" s="3">
-        <v>2106000</v>
+        <v>2141800</v>
       </c>
       <c r="H62" s="3">
-        <v>1862700</v>
+        <v>1894400</v>
       </c>
       <c r="I62" s="3">
-        <v>2613200</v>
+        <v>2657700</v>
       </c>
       <c r="J62" s="3">
-        <v>915500</v>
+        <v>931100</v>
       </c>
       <c r="K62" s="3">
         <v>964000</v>
@@ -2281,25 +2281,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>670354000</v>
+        <v>681751000</v>
       </c>
       <c r="E66" s="3">
-        <v>659825000</v>
+        <v>671043000</v>
       </c>
       <c r="F66" s="3">
-        <v>592129000</v>
+        <v>602196000</v>
       </c>
       <c r="G66" s="3">
-        <v>634706000</v>
+        <v>645497000</v>
       </c>
       <c r="H66" s="3">
-        <v>595469000</v>
+        <v>605593000</v>
       </c>
       <c r="I66" s="3">
-        <v>571894000</v>
+        <v>581617000</v>
       </c>
       <c r="J66" s="3">
-        <v>542423000</v>
+        <v>551646000</v>
       </c>
       <c r="K66" s="3">
         <v>555626000</v>
@@ -2445,25 +2445,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>27328000</v>
+        <v>27792600</v>
       </c>
       <c r="E72" s="3">
-        <v>25732500</v>
+        <v>26170000</v>
       </c>
       <c r="F72" s="3">
-        <v>23620000</v>
+        <v>24021600</v>
       </c>
       <c r="G72" s="3">
-        <v>21556700</v>
+        <v>21923200</v>
       </c>
       <c r="H72" s="3">
-        <v>21177000</v>
+        <v>21537000</v>
       </c>
       <c r="I72" s="3">
-        <v>20579800</v>
+        <v>20929700</v>
       </c>
       <c r="J72" s="3">
-        <v>19344000</v>
+        <v>19672900</v>
       </c>
       <c r="K72" s="3">
         <v>18172500</v>
@@ -2565,25 +2565,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>44982000</v>
+        <v>45746800</v>
       </c>
       <c r="E76" s="3">
-        <v>42641800</v>
+        <v>43366800</v>
       </c>
       <c r="F76" s="3">
-        <v>41191300</v>
+        <v>41891600</v>
       </c>
       <c r="G76" s="3">
-        <v>39652700</v>
+        <v>40326800</v>
       </c>
       <c r="H76" s="3">
-        <v>39326600</v>
+        <v>39995200</v>
       </c>
       <c r="I76" s="3">
-        <v>38344500</v>
+        <v>38996400</v>
       </c>
       <c r="J76" s="3">
-        <v>38146500</v>
+        <v>38795000</v>
       </c>
       <c r="K76" s="3">
         <v>37483400</v>
@@ -2660,25 +2660,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4592400</v>
+        <v>4670500</v>
       </c>
       <c r="E81" s="3">
-        <v>4606000</v>
+        <v>4684300</v>
       </c>
       <c r="F81" s="3">
-        <v>3986800</v>
+        <v>4054600</v>
       </c>
       <c r="G81" s="3">
-        <v>2314300</v>
+        <v>2353700</v>
       </c>
       <c r="H81" s="3">
-        <v>3851600</v>
+        <v>3917100</v>
       </c>
       <c r="I81" s="3">
-        <v>4140800</v>
+        <v>4211200</v>
       </c>
       <c r="J81" s="3">
-        <v>4144700</v>
+        <v>4215100</v>
       </c>
       <c r="K81" s="3">
         <v>3701100</v>
@@ -2704,25 +2704,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>597200</v>
+        <v>607300</v>
       </c>
       <c r="E83" s="3">
-        <v>652200</v>
+        <v>663300</v>
       </c>
       <c r="F83" s="3">
-        <v>703300</v>
+        <v>715200</v>
       </c>
       <c r="G83" s="3">
-        <v>900000</v>
+        <v>915300</v>
       </c>
       <c r="H83" s="3">
-        <v>563500</v>
+        <v>573100</v>
       </c>
       <c r="I83" s="3">
-        <v>775800</v>
+        <v>788900</v>
       </c>
       <c r="J83" s="3">
-        <v>628900</v>
+        <v>639600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -2884,25 +2884,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4197700</v>
+        <v>4269100</v>
       </c>
       <c r="E89" s="3">
-        <v>13053900</v>
+        <v>13275800</v>
       </c>
       <c r="F89" s="3">
-        <v>28352800</v>
+        <v>28834900</v>
       </c>
       <c r="G89" s="3">
-        <v>26062500</v>
+        <v>26505600</v>
       </c>
       <c r="H89" s="3">
-        <v>-2943900</v>
+        <v>-2993900</v>
       </c>
       <c r="I89" s="3">
-        <v>6836200</v>
+        <v>6952400</v>
       </c>
       <c r="J89" s="3">
-        <v>15558400</v>
+        <v>15822900</v>
       </c>
       <c r="K89" s="3">
         <v>7028200</v>
@@ -3018,25 +3018,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6913800</v>
+        <v>-7031400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1175600</v>
+        <v>-1195600</v>
       </c>
       <c r="F94" s="3">
-        <v>6636900</v>
+        <v>6749800</v>
       </c>
       <c r="G94" s="3">
-        <v>-7417900</v>
+        <v>-7544000</v>
       </c>
       <c r="H94" s="3">
-        <v>-133300</v>
+        <v>-135500</v>
       </c>
       <c r="I94" s="3">
-        <v>107400</v>
+        <v>109200</v>
       </c>
       <c r="J94" s="3">
-        <v>-8301000</v>
+        <v>-8442100</v>
       </c>
       <c r="K94" s="3">
         <v>-9342000</v>
@@ -3062,25 +3062,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2833900</v>
+        <v>-2882000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2448200</v>
+        <v>-2489900</v>
       </c>
       <c r="F96" s="3">
-        <v>-1833600</v>
+        <v>-1864800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1851100</v>
+        <v>-1882500</v>
       </c>
       <c r="H96" s="3">
-        <v>-2892700</v>
+        <v>-2941900</v>
       </c>
       <c r="I96" s="3">
-        <v>-2952300</v>
+        <v>-3002500</v>
       </c>
       <c r="J96" s="3">
-        <v>-2837700</v>
+        <v>-2886000</v>
       </c>
       <c r="K96" s="3">
         <v>-2958800</v>
@@ -3182,25 +3182,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2837100</v>
+        <v>2885300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1517200</v>
+        <v>-1543000</v>
       </c>
       <c r="F100" s="3">
-        <v>-6257800</v>
+        <v>-6364200</v>
       </c>
       <c r="G100" s="3">
-        <v>-279500</v>
+        <v>-284300</v>
       </c>
       <c r="H100" s="3">
-        <v>-1786400</v>
+        <v>-1816700</v>
       </c>
       <c r="I100" s="3">
-        <v>1695100</v>
+        <v>1724000</v>
       </c>
       <c r="J100" s="3">
-        <v>-4362100</v>
+        <v>-4436200</v>
       </c>
       <c r="K100" s="3">
         <v>1269400</v>
@@ -3212,25 +3212,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-106800</v>
+        <v>-108600</v>
       </c>
       <c r="E101" s="3">
-        <v>555100</v>
+        <v>564600</v>
       </c>
       <c r="F101" s="3">
-        <v>-692900</v>
+        <v>-704700</v>
       </c>
       <c r="G101" s="3">
-        <v>-1347700</v>
+        <v>-1370600</v>
       </c>
       <c r="H101" s="3">
-        <v>2700600</v>
+        <v>2746500</v>
       </c>
       <c r="I101" s="3">
-        <v>2305900</v>
+        <v>2345100</v>
       </c>
       <c r="J101" s="3">
-        <v>-1712600</v>
+        <v>-1741700</v>
       </c>
       <c r="K101" s="3">
         <v>-938100</v>
@@ -3242,25 +3242,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14200</v>
+        <v>14500</v>
       </c>
       <c r="E102" s="3">
-        <v>10916200</v>
+        <v>11101800</v>
       </c>
       <c r="F102" s="3">
-        <v>28039000</v>
+        <v>28515700</v>
       </c>
       <c r="G102" s="3">
-        <v>17017400</v>
+        <v>17306700</v>
       </c>
       <c r="H102" s="3">
-        <v>-2162900</v>
+        <v>-2199700</v>
       </c>
       <c r="I102" s="3">
-        <v>10944700</v>
+        <v>11130700</v>
       </c>
       <c r="J102" s="3">
-        <v>1182700</v>
+        <v>1202800</v>
       </c>
       <c r="K102" s="3">
         <v>-1982500</v>

--- a/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
@@ -711,25 +711,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>32835500</v>
+        <v>33249700</v>
       </c>
       <c r="E8" s="3">
-        <v>15534700</v>
+        <v>15730700</v>
       </c>
       <c r="F8" s="3">
-        <v>12850100</v>
+        <v>13012200</v>
       </c>
       <c r="G8" s="3">
-        <v>16072300</v>
+        <v>16275000</v>
       </c>
       <c r="H8" s="3">
-        <v>20448700</v>
+        <v>20706600</v>
       </c>
       <c r="I8" s="3">
-        <v>19955200</v>
+        <v>20206900</v>
       </c>
       <c r="J8" s="3">
-        <v>19161000</v>
+        <v>19402700</v>
       </c>
       <c r="K8" s="3">
         <v>19417200</v>
@@ -905,25 +905,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-332300</v>
+        <v>-336500</v>
       </c>
       <c r="E15" s="3">
-        <v>-380300</v>
+        <v>-385100</v>
       </c>
       <c r="F15" s="3">
-        <v>-419800</v>
+        <v>-425100</v>
       </c>
       <c r="G15" s="3">
-        <v>-564600</v>
+        <v>-571700</v>
       </c>
       <c r="H15" s="3">
-        <v>-456700</v>
+        <v>-462400</v>
       </c>
       <c r="I15" s="3">
-        <v>-651400</v>
+        <v>-659600</v>
       </c>
       <c r="J15" s="3">
-        <v>-474400</v>
+        <v>-480400</v>
       </c>
       <c r="K15" s="3">
         <v>-956200</v>
@@ -946,25 +946,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22086400</v>
+        <v>22365000</v>
       </c>
       <c r="E17" s="3">
-        <v>5595000</v>
+        <v>5665500</v>
       </c>
       <c r="F17" s="3">
-        <v>3159100</v>
+        <v>3198900</v>
       </c>
       <c r="G17" s="3">
-        <v>8629700</v>
+        <v>8738500</v>
       </c>
       <c r="H17" s="3">
-        <v>11536100</v>
+        <v>11681600</v>
       </c>
       <c r="I17" s="3">
-        <v>10857700</v>
+        <v>10994600</v>
       </c>
       <c r="J17" s="3">
-        <v>10161500</v>
+        <v>10289700</v>
       </c>
       <c r="K17" s="3">
         <v>10881700</v>
@@ -976,25 +976,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10749100</v>
+        <v>10884700</v>
       </c>
       <c r="E18" s="3">
-        <v>9939700</v>
+        <v>10065100</v>
       </c>
       <c r="F18" s="3">
-        <v>9691000</v>
+        <v>9813300</v>
       </c>
       <c r="G18" s="3">
-        <v>7442600</v>
+        <v>7536500</v>
       </c>
       <c r="H18" s="3">
-        <v>8912600</v>
+        <v>9025000</v>
       </c>
       <c r="I18" s="3">
-        <v>9097500</v>
+        <v>9212300</v>
       </c>
       <c r="J18" s="3">
-        <v>8999500</v>
+        <v>9113000</v>
       </c>
       <c r="K18" s="3">
         <v>8535500</v>
@@ -1020,25 +1020,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4119700</v>
+        <v>-4171700</v>
       </c>
       <c r="E20" s="3">
-        <v>-3307800</v>
+        <v>-3349500</v>
       </c>
       <c r="F20" s="3">
-        <v>-3811100</v>
+        <v>-3859200</v>
       </c>
       <c r="G20" s="3">
-        <v>-3813100</v>
+        <v>-3861200</v>
       </c>
       <c r="H20" s="3">
-        <v>-3043300</v>
+        <v>-3081600</v>
       </c>
       <c r="I20" s="3">
-        <v>-2586600</v>
+        <v>-2619200</v>
       </c>
       <c r="J20" s="3">
-        <v>-2924200</v>
+        <v>-2961000</v>
       </c>
       <c r="K20" s="3">
         <v>-3233700</v>
@@ -1050,25 +1050,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7240400</v>
+        <v>7323100</v>
       </c>
       <c r="E21" s="3">
-        <v>7299300</v>
+        <v>7381900</v>
       </c>
       <c r="F21" s="3">
-        <v>6599500</v>
+        <v>6672600</v>
       </c>
       <c r="G21" s="3">
-        <v>4550400</v>
+        <v>4594800</v>
       </c>
       <c r="H21" s="3">
-        <v>6446000</v>
+        <v>6519100</v>
       </c>
       <c r="I21" s="3">
-        <v>7304600</v>
+        <v>7385600</v>
       </c>
       <c r="J21" s="3">
-        <v>6718800</v>
+        <v>6794400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1110,25 +1110,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6629400</v>
+        <v>6713000</v>
       </c>
       <c r="E23" s="3">
-        <v>6632000</v>
+        <v>6715600</v>
       </c>
       <c r="F23" s="3">
-        <v>5879900</v>
+        <v>5954100</v>
       </c>
       <c r="G23" s="3">
-        <v>3629500</v>
+        <v>3675300</v>
       </c>
       <c r="H23" s="3">
-        <v>5869400</v>
+        <v>5943400</v>
       </c>
       <c r="I23" s="3">
-        <v>6510900</v>
+        <v>6593000</v>
       </c>
       <c r="J23" s="3">
-        <v>6075300</v>
+        <v>6151900</v>
       </c>
       <c r="K23" s="3">
         <v>5301800</v>
@@ -1140,25 +1140,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1940400</v>
+        <v>1964900</v>
       </c>
       <c r="E24" s="3">
-        <v>1934500</v>
+        <v>1958900</v>
       </c>
       <c r="F24" s="3">
-        <v>1813400</v>
+        <v>1836300</v>
       </c>
       <c r="G24" s="3">
-        <v>1210700</v>
+        <v>1226000</v>
       </c>
       <c r="H24" s="3">
-        <v>1716700</v>
+        <v>1738400</v>
       </c>
       <c r="I24" s="3">
-        <v>1831900</v>
+        <v>1855000</v>
       </c>
       <c r="J24" s="3">
-        <v>1891100</v>
+        <v>1914900</v>
       </c>
       <c r="K24" s="3">
         <v>1593500</v>
@@ -1200,25 +1200,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4688900</v>
+        <v>4748100</v>
       </c>
       <c r="E26" s="3">
-        <v>4697500</v>
+        <v>4756700</v>
       </c>
       <c r="F26" s="3">
-        <v>4066400</v>
+        <v>4117700</v>
       </c>
       <c r="G26" s="3">
-        <v>2418800</v>
+        <v>2449300</v>
       </c>
       <c r="H26" s="3">
-        <v>4152600</v>
+        <v>4205000</v>
       </c>
       <c r="I26" s="3">
-        <v>4679000</v>
+        <v>4738100</v>
       </c>
       <c r="J26" s="3">
-        <v>4184200</v>
+        <v>4237000</v>
       </c>
       <c r="K26" s="3">
         <v>3708300</v>
@@ -1230,25 +1230,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4670500</v>
+        <v>4729400</v>
       </c>
       <c r="E27" s="3">
-        <v>4696800</v>
+        <v>4756000</v>
       </c>
       <c r="F27" s="3">
-        <v>4065800</v>
+        <v>4117100</v>
       </c>
       <c r="G27" s="3">
-        <v>2418200</v>
+        <v>2448700</v>
       </c>
       <c r="H27" s="3">
-        <v>4142800</v>
+        <v>4195000</v>
       </c>
       <c r="I27" s="3">
-        <v>4668500</v>
+        <v>4727400</v>
       </c>
       <c r="J27" s="3">
-        <v>4174400</v>
+        <v>4227000</v>
       </c>
       <c r="K27" s="3">
         <v>3701100</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-12500</v>
+        <v>-12700</v>
       </c>
       <c r="F29" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="G29" s="3">
-        <v>-64500</v>
+        <v>-65300</v>
       </c>
       <c r="H29" s="3">
-        <v>-225700</v>
+        <v>-228500</v>
       </c>
       <c r="I29" s="3">
-        <v>-457300</v>
+        <v>-463100</v>
       </c>
       <c r="J29" s="3">
-        <v>40800</v>
+        <v>41300</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1380,25 +1380,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4119700</v>
+        <v>4171700</v>
       </c>
       <c r="E32" s="3">
-        <v>3307800</v>
+        <v>3349500</v>
       </c>
       <c r="F32" s="3">
-        <v>3811100</v>
+        <v>3859200</v>
       </c>
       <c r="G32" s="3">
-        <v>3813100</v>
+        <v>3861200</v>
       </c>
       <c r="H32" s="3">
-        <v>3043300</v>
+        <v>3081600</v>
       </c>
       <c r="I32" s="3">
-        <v>2586600</v>
+        <v>2619200</v>
       </c>
       <c r="J32" s="3">
-        <v>2924200</v>
+        <v>2961000</v>
       </c>
       <c r="K32" s="3">
         <v>3233700</v>
@@ -1410,25 +1410,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4670500</v>
+        <v>4729400</v>
       </c>
       <c r="E33" s="3">
-        <v>4684300</v>
+        <v>4743400</v>
       </c>
       <c r="F33" s="3">
-        <v>4054600</v>
+        <v>4105700</v>
       </c>
       <c r="G33" s="3">
-        <v>2353700</v>
+        <v>2383400</v>
       </c>
       <c r="H33" s="3">
-        <v>3917100</v>
+        <v>3966500</v>
       </c>
       <c r="I33" s="3">
-        <v>4211200</v>
+        <v>4264300</v>
       </c>
       <c r="J33" s="3">
-        <v>4215100</v>
+        <v>4268300</v>
       </c>
       <c r="K33" s="3">
         <v>3701100</v>
@@ -1470,25 +1470,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4670500</v>
+        <v>4729400</v>
       </c>
       <c r="E35" s="3">
-        <v>4684300</v>
+        <v>4743400</v>
       </c>
       <c r="F35" s="3">
-        <v>4054600</v>
+        <v>4105700</v>
       </c>
       <c r="G35" s="3">
-        <v>2353700</v>
+        <v>2383400</v>
       </c>
       <c r="H35" s="3">
-        <v>3917100</v>
+        <v>3966500</v>
       </c>
       <c r="I35" s="3">
-        <v>4211200</v>
+        <v>4264300</v>
       </c>
       <c r="J35" s="3">
-        <v>4215100</v>
+        <v>4268300</v>
       </c>
       <c r="K35" s="3">
         <v>3701100</v>
@@ -1563,25 +1563,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100009000</v>
+        <v>213312000</v>
       </c>
       <c r="E41" s="3">
-        <v>107120000</v>
+        <v>108471000</v>
       </c>
       <c r="F41" s="3">
-        <v>96890500</v>
+        <v>98112700</v>
       </c>
       <c r="G41" s="3">
-        <v>56506400</v>
+        <v>57219200</v>
       </c>
       <c r="H41" s="3">
-        <v>44892700</v>
+        <v>45459000</v>
       </c>
       <c r="I41" s="3">
-        <v>99462000</v>
+        <v>100717000</v>
       </c>
       <c r="J41" s="3">
-        <v>40351800</v>
+        <v>40860800</v>
       </c>
       <c r="K41" s="3">
         <v>38753400</v>
@@ -1593,25 +1593,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>90592800</v>
+        <v>91735500</v>
       </c>
       <c r="E42" s="3">
-        <v>101402000</v>
+        <v>102682000</v>
       </c>
       <c r="F42" s="3">
-        <v>72485900</v>
+        <v>73400300</v>
       </c>
       <c r="G42" s="3">
-        <v>155390000</v>
+        <v>157350000</v>
       </c>
       <c r="H42" s="3">
-        <v>134312000</v>
+        <v>136007000</v>
       </c>
       <c r="I42" s="3">
-        <v>95781100</v>
+        <v>96989300</v>
       </c>
       <c r="J42" s="3">
-        <v>89946600</v>
+        <v>91081200</v>
       </c>
       <c r="K42" s="3">
         <v>109372000</v>
@@ -1743,25 +1743,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1545600</v>
+        <v>1565100</v>
       </c>
       <c r="E47" s="3">
-        <v>1435100</v>
+        <v>1453200</v>
       </c>
       <c r="F47" s="3">
-        <v>1297600</v>
+        <v>1313900</v>
       </c>
       <c r="G47" s="3">
-        <v>1423900</v>
+        <v>1441900</v>
       </c>
       <c r="H47" s="3">
-        <v>1945700</v>
+        <v>1970200</v>
       </c>
       <c r="I47" s="3">
-        <v>1679900</v>
+        <v>1701100</v>
       </c>
       <c r="J47" s="3">
-        <v>1479200</v>
+        <v>1497800</v>
       </c>
       <c r="K47" s="3">
         <v>2769500</v>
@@ -1773,25 +1773,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1350900</v>
+        <v>1367900</v>
       </c>
       <c r="E48" s="3">
-        <v>1599600</v>
+        <v>1619800</v>
       </c>
       <c r="F48" s="3">
-        <v>1799000</v>
+        <v>1821700</v>
       </c>
       <c r="G48" s="3">
-        <v>1982600</v>
+        <v>2007600</v>
       </c>
       <c r="H48" s="3">
-        <v>1266000</v>
+        <v>1282000</v>
       </c>
       <c r="I48" s="3">
-        <v>1206100</v>
+        <v>1221300</v>
       </c>
       <c r="J48" s="3">
-        <v>1293000</v>
+        <v>1309300</v>
       </c>
       <c r="K48" s="3">
         <v>1429500</v>
@@ -1803,25 +1803,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2670200</v>
+        <v>5407700</v>
       </c>
       <c r="E49" s="3">
-        <v>2551100</v>
+        <v>2583200</v>
       </c>
       <c r="F49" s="3">
-        <v>2713600</v>
+        <v>2747800</v>
       </c>
       <c r="G49" s="3">
-        <v>2881400</v>
+        <v>2917700</v>
       </c>
       <c r="H49" s="3">
-        <v>3198500</v>
+        <v>3238900</v>
       </c>
       <c r="I49" s="3">
-        <v>6487900</v>
+        <v>6569700</v>
       </c>
       <c r="J49" s="3">
-        <v>4586300</v>
+        <v>4644100</v>
       </c>
       <c r="K49" s="3">
         <v>4973800</v>
@@ -1893,25 +1893,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2195100</v>
+        <v>2230800</v>
       </c>
       <c r="E52" s="3">
-        <v>2226700</v>
+        <v>2254800</v>
       </c>
       <c r="F52" s="3">
-        <v>1539100</v>
+        <v>1558500</v>
       </c>
       <c r="G52" s="3">
-        <v>1397600</v>
+        <v>1415200</v>
       </c>
       <c r="H52" s="3">
-        <v>2097000</v>
+        <v>2123500</v>
       </c>
       <c r="I52" s="3">
-        <v>29655400</v>
+        <v>30029500</v>
       </c>
       <c r="J52" s="3">
-        <v>5688400</v>
+        <v>5760200</v>
       </c>
       <c r="K52" s="3">
         <v>403900</v>
@@ -1953,25 +1953,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>727498000</v>
+        <v>736690000</v>
       </c>
       <c r="E54" s="3">
-        <v>714410000</v>
+        <v>723421000</v>
       </c>
       <c r="F54" s="3">
-        <v>644088000</v>
+        <v>652212000</v>
       </c>
       <c r="G54" s="3">
-        <v>685824000</v>
+        <v>694475000</v>
       </c>
       <c r="H54" s="3">
-        <v>645588000</v>
+        <v>653732000</v>
       </c>
       <c r="I54" s="3">
-        <v>620614000</v>
+        <v>628442000</v>
       </c>
       <c r="J54" s="3">
-        <v>590441000</v>
+        <v>597888000</v>
       </c>
       <c r="K54" s="3">
         <v>593110000</v>
@@ -2011,25 +2011,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9899600</v>
+        <v>10059100</v>
       </c>
       <c r="E57" s="3">
-        <v>6471400</v>
+        <v>6553100</v>
       </c>
       <c r="F57" s="3">
-        <v>5689700</v>
+        <v>5761500</v>
       </c>
       <c r="G57" s="3">
-        <v>6006200</v>
+        <v>6082000</v>
       </c>
       <c r="H57" s="3">
-        <v>5242900</v>
+        <v>5309100</v>
       </c>
       <c r="I57" s="3">
-        <v>4536300</v>
+        <v>4593500</v>
       </c>
       <c r="J57" s="3">
-        <v>5494300</v>
+        <v>5563600</v>
       </c>
       <c r="K57" s="3">
         <v>1052200</v>
@@ -2071,25 +2071,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200700</v>
+        <v>203200</v>
       </c>
       <c r="E59" s="3">
-        <v>545500</v>
+        <v>552400</v>
       </c>
       <c r="F59" s="3">
-        <v>275700</v>
+        <v>279200</v>
       </c>
       <c r="G59" s="3">
-        <v>229600</v>
+        <v>232500</v>
       </c>
       <c r="H59" s="3">
-        <v>171100</v>
+        <v>173200</v>
       </c>
       <c r="I59" s="3">
-        <v>197400</v>
+        <v>199900</v>
       </c>
       <c r="J59" s="3">
-        <v>158600</v>
+        <v>160600</v>
       </c>
       <c r="K59" s="3">
         <v>2063500</v>
@@ -2131,25 +2131,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>76337200</v>
+        <v>77300100</v>
       </c>
       <c r="E61" s="3">
-        <v>61677000</v>
+        <v>62455000</v>
       </c>
       <c r="F61" s="3">
-        <v>66493500</v>
+        <v>67332300</v>
       </c>
       <c r="G61" s="3">
-        <v>78741500</v>
+        <v>79734800</v>
       </c>
       <c r="H61" s="3">
-        <v>85336700</v>
+        <v>86413100</v>
       </c>
       <c r="I61" s="3">
-        <v>79735800</v>
+        <v>80741600</v>
       </c>
       <c r="J61" s="3">
-        <v>71046200</v>
+        <v>71942400</v>
       </c>
       <c r="K61" s="3">
         <v>74270500</v>
@@ -2161,25 +2161,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1558100</v>
+        <v>1577800</v>
       </c>
       <c r="E62" s="3">
-        <v>1647600</v>
+        <v>1668400</v>
       </c>
       <c r="F62" s="3">
-        <v>1899000</v>
+        <v>1922900</v>
       </c>
       <c r="G62" s="3">
-        <v>2141800</v>
+        <v>2168800</v>
       </c>
       <c r="H62" s="3">
-        <v>1894400</v>
+        <v>1918300</v>
       </c>
       <c r="I62" s="3">
-        <v>2657700</v>
+        <v>2691200</v>
       </c>
       <c r="J62" s="3">
-        <v>931100</v>
+        <v>942800</v>
       </c>
       <c r="K62" s="3">
         <v>964000</v>
@@ -2281,25 +2281,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>681751000</v>
+        <v>690385000</v>
       </c>
       <c r="E66" s="3">
-        <v>671043000</v>
+        <v>679507000</v>
       </c>
       <c r="F66" s="3">
-        <v>602196000</v>
+        <v>609792000</v>
       </c>
       <c r="G66" s="3">
-        <v>645497000</v>
+        <v>653640000</v>
       </c>
       <c r="H66" s="3">
-        <v>605593000</v>
+        <v>613232000</v>
       </c>
       <c r="I66" s="3">
-        <v>581617000</v>
+        <v>588954000</v>
       </c>
       <c r="J66" s="3">
-        <v>551646000</v>
+        <v>558604000</v>
       </c>
       <c r="K66" s="3">
         <v>555626000</v>
@@ -2445,25 +2445,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>27792600</v>
+        <v>28123900</v>
       </c>
       <c r="E72" s="3">
-        <v>26170000</v>
+        <v>26500100</v>
       </c>
       <c r="F72" s="3">
-        <v>24021600</v>
+        <v>24324600</v>
       </c>
       <c r="G72" s="3">
-        <v>21923200</v>
+        <v>22199800</v>
       </c>
       <c r="H72" s="3">
-        <v>21537000</v>
+        <v>21808700</v>
       </c>
       <c r="I72" s="3">
-        <v>20929700</v>
+        <v>21193700</v>
       </c>
       <c r="J72" s="3">
-        <v>19672900</v>
+        <v>19921000</v>
       </c>
       <c r="K72" s="3">
         <v>18172500</v>
@@ -2565,25 +2565,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>45746800</v>
+        <v>46304500</v>
       </c>
       <c r="E76" s="3">
-        <v>43366800</v>
+        <v>43913800</v>
       </c>
       <c r="F76" s="3">
-        <v>41891600</v>
+        <v>42420000</v>
       </c>
       <c r="G76" s="3">
-        <v>40326800</v>
+        <v>40835500</v>
       </c>
       <c r="H76" s="3">
-        <v>39995200</v>
+        <v>40499700</v>
       </c>
       <c r="I76" s="3">
-        <v>38996400</v>
+        <v>39488300</v>
       </c>
       <c r="J76" s="3">
-        <v>38795000</v>
+        <v>39284400</v>
       </c>
       <c r="K76" s="3">
         <v>37483400</v>
@@ -2660,25 +2660,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4670500</v>
+        <v>4729400</v>
       </c>
       <c r="E81" s="3">
-        <v>4684300</v>
+        <v>4743400</v>
       </c>
       <c r="F81" s="3">
-        <v>4054600</v>
+        <v>4105700</v>
       </c>
       <c r="G81" s="3">
-        <v>2353700</v>
+        <v>2383400</v>
       </c>
       <c r="H81" s="3">
-        <v>3917100</v>
+        <v>3966500</v>
       </c>
       <c r="I81" s="3">
-        <v>4211200</v>
+        <v>4264300</v>
       </c>
       <c r="J81" s="3">
-        <v>4215100</v>
+        <v>4268300</v>
       </c>
       <c r="K81" s="3">
         <v>3701100</v>
@@ -2704,25 +2704,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>607300</v>
+        <v>615000</v>
       </c>
       <c r="E83" s="3">
-        <v>663300</v>
+        <v>671600</v>
       </c>
       <c r="F83" s="3">
-        <v>715200</v>
+        <v>724300</v>
       </c>
       <c r="G83" s="3">
-        <v>915300</v>
+        <v>926800</v>
       </c>
       <c r="H83" s="3">
-        <v>573100</v>
+        <v>580300</v>
       </c>
       <c r="I83" s="3">
-        <v>788900</v>
+        <v>798900</v>
       </c>
       <c r="J83" s="3">
-        <v>639600</v>
+        <v>647600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -2884,25 +2884,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4269100</v>
+        <v>4323000</v>
       </c>
       <c r="E89" s="3">
-        <v>13275800</v>
+        <v>13443300</v>
       </c>
       <c r="F89" s="3">
-        <v>28834900</v>
+        <v>29198600</v>
       </c>
       <c r="G89" s="3">
-        <v>26505600</v>
+        <v>26839900</v>
       </c>
       <c r="H89" s="3">
-        <v>-2993900</v>
+        <v>-3031700</v>
       </c>
       <c r="I89" s="3">
-        <v>6952400</v>
+        <v>7040100</v>
       </c>
       <c r="J89" s="3">
-        <v>15822900</v>
+        <v>16022500</v>
       </c>
       <c r="K89" s="3">
         <v>7028200</v>
@@ -3018,25 +3018,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7031400</v>
+        <v>-7120100</v>
       </c>
       <c r="E94" s="3">
-        <v>-1195600</v>
+        <v>-1210700</v>
       </c>
       <c r="F94" s="3">
-        <v>6749800</v>
+        <v>6834900</v>
       </c>
       <c r="G94" s="3">
-        <v>-7544000</v>
+        <v>-7639100</v>
       </c>
       <c r="H94" s="3">
-        <v>-135500</v>
+        <v>-137300</v>
       </c>
       <c r="I94" s="3">
-        <v>109200</v>
+        <v>110600</v>
       </c>
       <c r="J94" s="3">
-        <v>-8442100</v>
+        <v>-8548600</v>
       </c>
       <c r="K94" s="3">
         <v>-9342000</v>
@@ -3062,25 +3062,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2882000</v>
+        <v>-2918400</v>
       </c>
       <c r="E96" s="3">
-        <v>-2489900</v>
+        <v>-2521300</v>
       </c>
       <c r="F96" s="3">
-        <v>-1864800</v>
+        <v>-1888300</v>
       </c>
       <c r="G96" s="3">
-        <v>-1882500</v>
+        <v>-1906300</v>
       </c>
       <c r="H96" s="3">
-        <v>-2941900</v>
+        <v>-2979000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3002500</v>
+        <v>-3040300</v>
       </c>
       <c r="J96" s="3">
-        <v>-2886000</v>
+        <v>-2922400</v>
       </c>
       <c r="K96" s="3">
         <v>-2958800</v>
@@ -3182,25 +3182,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2885300</v>
+        <v>2921700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1543000</v>
+        <v>-1562500</v>
       </c>
       <c r="F100" s="3">
-        <v>-6364200</v>
+        <v>-6444500</v>
       </c>
       <c r="G100" s="3">
-        <v>-284300</v>
+        <v>-287800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1816700</v>
+        <v>-1839700</v>
       </c>
       <c r="I100" s="3">
-        <v>1724000</v>
+        <v>1745700</v>
       </c>
       <c r="J100" s="3">
-        <v>-4436200</v>
+        <v>-4492200</v>
       </c>
       <c r="K100" s="3">
         <v>1269400</v>
@@ -3212,25 +3212,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-108600</v>
+        <v>-109900</v>
       </c>
       <c r="E101" s="3">
-        <v>564600</v>
+        <v>571700</v>
       </c>
       <c r="F101" s="3">
-        <v>-704700</v>
+        <v>-713600</v>
       </c>
       <c r="G101" s="3">
-        <v>-1370600</v>
+        <v>-1387900</v>
       </c>
       <c r="H101" s="3">
-        <v>2746500</v>
+        <v>2781100</v>
       </c>
       <c r="I101" s="3">
-        <v>2345100</v>
+        <v>2374700</v>
       </c>
       <c r="J101" s="3">
-        <v>-1741700</v>
+        <v>-1763700</v>
       </c>
       <c r="K101" s="3">
         <v>-938100</v>
@@ -3242,25 +3242,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14500</v>
+        <v>14700</v>
       </c>
       <c r="E102" s="3">
-        <v>11101800</v>
+        <v>11241800</v>
       </c>
       <c r="F102" s="3">
-        <v>28515700</v>
+        <v>28875400</v>
       </c>
       <c r="G102" s="3">
-        <v>17306700</v>
+        <v>17525000</v>
       </c>
       <c r="H102" s="3">
-        <v>-2199700</v>
+        <v>-2227400</v>
       </c>
       <c r="I102" s="3">
-        <v>11130700</v>
+        <v>11271100</v>
       </c>
       <c r="J102" s="3">
-        <v>1202800</v>
+        <v>1218000</v>
       </c>
       <c r="K102" s="3">
         <v>-1982500</v>

--- a/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
@@ -711,25 +711,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>33249700</v>
+        <v>33449300</v>
       </c>
       <c r="E8" s="3">
-        <v>15730700</v>
+        <v>15825100</v>
       </c>
       <c r="F8" s="3">
-        <v>13012200</v>
+        <v>13090300</v>
       </c>
       <c r="G8" s="3">
-        <v>16275000</v>
+        <v>16372700</v>
       </c>
       <c r="H8" s="3">
-        <v>20706600</v>
+        <v>20830900</v>
       </c>
       <c r="I8" s="3">
-        <v>20206900</v>
+        <v>20328200</v>
       </c>
       <c r="J8" s="3">
-        <v>19402700</v>
+        <v>19519100</v>
       </c>
       <c r="K8" s="3">
         <v>19417200</v>
@@ -905,25 +905,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-336500</v>
+        <v>-338500</v>
       </c>
       <c r="E15" s="3">
-        <v>-385100</v>
+        <v>-387400</v>
       </c>
       <c r="F15" s="3">
-        <v>-425100</v>
+        <v>-427700</v>
       </c>
       <c r="G15" s="3">
-        <v>-571700</v>
+        <v>-575100</v>
       </c>
       <c r="H15" s="3">
-        <v>-462400</v>
+        <v>-465200</v>
       </c>
       <c r="I15" s="3">
-        <v>-659600</v>
+        <v>-663600</v>
       </c>
       <c r="J15" s="3">
-        <v>-480400</v>
+        <v>-483300</v>
       </c>
       <c r="K15" s="3">
         <v>-956200</v>
@@ -946,25 +946,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22365000</v>
+        <v>22499300</v>
       </c>
       <c r="E17" s="3">
-        <v>5665500</v>
+        <v>5699600</v>
       </c>
       <c r="F17" s="3">
-        <v>3198900</v>
+        <v>3218100</v>
       </c>
       <c r="G17" s="3">
-        <v>8738500</v>
+        <v>8791000</v>
       </c>
       <c r="H17" s="3">
-        <v>11681600</v>
+        <v>11751700</v>
       </c>
       <c r="I17" s="3">
-        <v>10994600</v>
+        <v>11060600</v>
       </c>
       <c r="J17" s="3">
-        <v>10289700</v>
+        <v>10351400</v>
       </c>
       <c r="K17" s="3">
         <v>10881700</v>
@@ -976,25 +976,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10884700</v>
+        <v>10950000</v>
       </c>
       <c r="E18" s="3">
-        <v>10065100</v>
+        <v>10125600</v>
       </c>
       <c r="F18" s="3">
-        <v>9813300</v>
+        <v>9872200</v>
       </c>
       <c r="G18" s="3">
-        <v>7536500</v>
+        <v>7581800</v>
       </c>
       <c r="H18" s="3">
-        <v>9025000</v>
+        <v>9079200</v>
       </c>
       <c r="I18" s="3">
-        <v>9212300</v>
+        <v>9267600</v>
       </c>
       <c r="J18" s="3">
-        <v>9113000</v>
+        <v>9167700</v>
       </c>
       <c r="K18" s="3">
         <v>8535500</v>
@@ -1020,25 +1020,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4171700</v>
+        <v>-4196700</v>
       </c>
       <c r="E20" s="3">
-        <v>-3349500</v>
+        <v>-3369600</v>
       </c>
       <c r="F20" s="3">
-        <v>-3859200</v>
+        <v>-3882400</v>
       </c>
       <c r="G20" s="3">
-        <v>-3861200</v>
+        <v>-3884400</v>
       </c>
       <c r="H20" s="3">
-        <v>-3081600</v>
+        <v>-3100100</v>
       </c>
       <c r="I20" s="3">
-        <v>-2619200</v>
+        <v>-2634900</v>
       </c>
       <c r="J20" s="3">
-        <v>-2961000</v>
+        <v>-2978800</v>
       </c>
       <c r="K20" s="3">
         <v>-3233700</v>
@@ -1050,25 +1050,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7323100</v>
+        <v>7373700</v>
       </c>
       <c r="E21" s="3">
-        <v>7381900</v>
+        <v>7433500</v>
       </c>
       <c r="F21" s="3">
-        <v>6672600</v>
+        <v>6720500</v>
       </c>
       <c r="G21" s="3">
-        <v>4594800</v>
+        <v>4632400</v>
       </c>
       <c r="H21" s="3">
-        <v>6519100</v>
+        <v>6564600</v>
       </c>
       <c r="I21" s="3">
-        <v>7385600</v>
+        <v>7438600</v>
       </c>
       <c r="J21" s="3">
-        <v>6794400</v>
+        <v>6842300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1110,25 +1110,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6713000</v>
+        <v>6753300</v>
       </c>
       <c r="E23" s="3">
-        <v>6715600</v>
+        <v>6756000</v>
       </c>
       <c r="F23" s="3">
-        <v>5954100</v>
+        <v>5989800</v>
       </c>
       <c r="G23" s="3">
-        <v>3675300</v>
+        <v>3697400</v>
       </c>
       <c r="H23" s="3">
-        <v>5943400</v>
+        <v>5979100</v>
       </c>
       <c r="I23" s="3">
-        <v>6593000</v>
+        <v>6632600</v>
       </c>
       <c r="J23" s="3">
-        <v>6151900</v>
+        <v>6188900</v>
       </c>
       <c r="K23" s="3">
         <v>5301800</v>
@@ -1140,25 +1140,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1964900</v>
+        <v>1976700</v>
       </c>
       <c r="E24" s="3">
-        <v>1958900</v>
+        <v>1970700</v>
       </c>
       <c r="F24" s="3">
-        <v>1836300</v>
+        <v>1847300</v>
       </c>
       <c r="G24" s="3">
-        <v>1226000</v>
+        <v>1233400</v>
       </c>
       <c r="H24" s="3">
-        <v>1738400</v>
+        <v>1748800</v>
       </c>
       <c r="I24" s="3">
-        <v>1855000</v>
+        <v>1866100</v>
       </c>
       <c r="J24" s="3">
-        <v>1914900</v>
+        <v>1926400</v>
       </c>
       <c r="K24" s="3">
         <v>1593500</v>
@@ -1200,25 +1200,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4748100</v>
+        <v>4776600</v>
       </c>
       <c r="E26" s="3">
-        <v>4756700</v>
+        <v>4785300</v>
       </c>
       <c r="F26" s="3">
-        <v>4117700</v>
+        <v>4142500</v>
       </c>
       <c r="G26" s="3">
-        <v>2449300</v>
+        <v>2464000</v>
       </c>
       <c r="H26" s="3">
-        <v>4205000</v>
+        <v>4230300</v>
       </c>
       <c r="I26" s="3">
-        <v>4738100</v>
+        <v>4766500</v>
       </c>
       <c r="J26" s="3">
-        <v>4237000</v>
+        <v>4262400</v>
       </c>
       <c r="K26" s="3">
         <v>3708300</v>
@@ -1230,25 +1230,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4729400</v>
+        <v>4757800</v>
       </c>
       <c r="E27" s="3">
-        <v>4756000</v>
+        <v>4784600</v>
       </c>
       <c r="F27" s="3">
-        <v>4117100</v>
+        <v>4141800</v>
       </c>
       <c r="G27" s="3">
-        <v>2448700</v>
+        <v>2463400</v>
       </c>
       <c r="H27" s="3">
-        <v>4195000</v>
+        <v>4220200</v>
       </c>
       <c r="I27" s="3">
-        <v>4727400</v>
+        <v>4755800</v>
       </c>
       <c r="J27" s="3">
-        <v>4227000</v>
+        <v>4252400</v>
       </c>
       <c r="K27" s="3">
         <v>3701100</v>
@@ -1296,19 +1296,19 @@
         <v>-12700</v>
       </c>
       <c r="F29" s="3">
-        <v>-11300</v>
+        <v>-11400</v>
       </c>
       <c r="G29" s="3">
-        <v>-65300</v>
+        <v>-65700</v>
       </c>
       <c r="H29" s="3">
-        <v>-228500</v>
+        <v>-229900</v>
       </c>
       <c r="I29" s="3">
-        <v>-463100</v>
+        <v>-465900</v>
       </c>
       <c r="J29" s="3">
-        <v>41300</v>
+        <v>41600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1380,25 +1380,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4171700</v>
+        <v>4196700</v>
       </c>
       <c r="E32" s="3">
-        <v>3349500</v>
+        <v>3369600</v>
       </c>
       <c r="F32" s="3">
-        <v>3859200</v>
+        <v>3882400</v>
       </c>
       <c r="G32" s="3">
-        <v>3861200</v>
+        <v>3884400</v>
       </c>
       <c r="H32" s="3">
-        <v>3081600</v>
+        <v>3100100</v>
       </c>
       <c r="I32" s="3">
-        <v>2619200</v>
+        <v>2634900</v>
       </c>
       <c r="J32" s="3">
-        <v>2961000</v>
+        <v>2978800</v>
       </c>
       <c r="K32" s="3">
         <v>3233700</v>
@@ -1410,25 +1410,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4729400</v>
+        <v>4757800</v>
       </c>
       <c r="E33" s="3">
-        <v>4743400</v>
+        <v>4771900</v>
       </c>
       <c r="F33" s="3">
-        <v>4105700</v>
+        <v>4130400</v>
       </c>
       <c r="G33" s="3">
-        <v>2383400</v>
+        <v>2397700</v>
       </c>
       <c r="H33" s="3">
-        <v>3966500</v>
+        <v>3990300</v>
       </c>
       <c r="I33" s="3">
-        <v>4264300</v>
+        <v>4289900</v>
       </c>
       <c r="J33" s="3">
-        <v>4268300</v>
+        <v>4293900</v>
       </c>
       <c r="K33" s="3">
         <v>3701100</v>
@@ -1470,25 +1470,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4729400</v>
+        <v>4757800</v>
       </c>
       <c r="E35" s="3">
-        <v>4743400</v>
+        <v>4771900</v>
       </c>
       <c r="F35" s="3">
-        <v>4105700</v>
+        <v>4130400</v>
       </c>
       <c r="G35" s="3">
-        <v>2383400</v>
+        <v>2397700</v>
       </c>
       <c r="H35" s="3">
-        <v>3966500</v>
+        <v>3990300</v>
       </c>
       <c r="I35" s="3">
-        <v>4264300</v>
+        <v>4289900</v>
       </c>
       <c r="J35" s="3">
-        <v>4268300</v>
+        <v>4293900</v>
       </c>
       <c r="K35" s="3">
         <v>3701100</v>
@@ -1563,25 +1563,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>213312000</v>
+        <v>214593000</v>
       </c>
       <c r="E41" s="3">
-        <v>108471000</v>
+        <v>109122000</v>
       </c>
       <c r="F41" s="3">
-        <v>98112700</v>
+        <v>98701700</v>
       </c>
       <c r="G41" s="3">
-        <v>57219200</v>
+        <v>57562700</v>
       </c>
       <c r="H41" s="3">
-        <v>45459000</v>
+        <v>45731900</v>
       </c>
       <c r="I41" s="3">
-        <v>100717000</v>
+        <v>101321000</v>
       </c>
       <c r="J41" s="3">
-        <v>40860800</v>
+        <v>41106100</v>
       </c>
       <c r="K41" s="3">
         <v>38753400</v>
@@ -1593,25 +1593,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>91735500</v>
+        <v>92286200</v>
       </c>
       <c r="E42" s="3">
-        <v>102682000</v>
+        <v>103298000</v>
       </c>
       <c r="F42" s="3">
-        <v>73400300</v>
+        <v>73840900</v>
       </c>
       <c r="G42" s="3">
-        <v>157350000</v>
+        <v>158295000</v>
       </c>
       <c r="H42" s="3">
-        <v>136007000</v>
+        <v>136823000</v>
       </c>
       <c r="I42" s="3">
-        <v>96989300</v>
+        <v>97571500</v>
       </c>
       <c r="J42" s="3">
-        <v>91081200</v>
+        <v>91628000</v>
       </c>
       <c r="K42" s="3">
         <v>109372000</v>
@@ -1743,25 +1743,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1565100</v>
+        <v>1574500</v>
       </c>
       <c r="E47" s="3">
-        <v>1453200</v>
+        <v>1461900</v>
       </c>
       <c r="F47" s="3">
-        <v>1313900</v>
+        <v>1321800</v>
       </c>
       <c r="G47" s="3">
-        <v>1441900</v>
+        <v>1450500</v>
       </c>
       <c r="H47" s="3">
-        <v>1970200</v>
+        <v>1982100</v>
       </c>
       <c r="I47" s="3">
-        <v>1701100</v>
+        <v>1711300</v>
       </c>
       <c r="J47" s="3">
-        <v>1497800</v>
+        <v>1506800</v>
       </c>
       <c r="K47" s="3">
         <v>2769500</v>
@@ -1773,25 +1773,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1367900</v>
+        <v>1376100</v>
       </c>
       <c r="E48" s="3">
-        <v>1619800</v>
+        <v>1629500</v>
       </c>
       <c r="F48" s="3">
-        <v>1821700</v>
+        <v>1832600</v>
       </c>
       <c r="G48" s="3">
-        <v>2007600</v>
+        <v>2019600</v>
       </c>
       <c r="H48" s="3">
-        <v>1282000</v>
+        <v>1289700</v>
       </c>
       <c r="I48" s="3">
-        <v>1221300</v>
+        <v>1228700</v>
       </c>
       <c r="J48" s="3">
-        <v>1309300</v>
+        <v>1317100</v>
       </c>
       <c r="K48" s="3">
         <v>1429500</v>
@@ -1803,25 +1803,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5407700</v>
+        <v>5440200</v>
       </c>
       <c r="E49" s="3">
-        <v>2583200</v>
+        <v>2598800</v>
       </c>
       <c r="F49" s="3">
-        <v>2747800</v>
+        <v>2764300</v>
       </c>
       <c r="G49" s="3">
-        <v>2917700</v>
+        <v>2935200</v>
       </c>
       <c r="H49" s="3">
-        <v>3238900</v>
+        <v>3258300</v>
       </c>
       <c r="I49" s="3">
-        <v>6569700</v>
+        <v>6609200</v>
       </c>
       <c r="J49" s="3">
-        <v>4644100</v>
+        <v>4672000</v>
       </c>
       <c r="K49" s="3">
         <v>4973800</v>
@@ -1893,25 +1893,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2230800</v>
+        <v>2244200</v>
       </c>
       <c r="E52" s="3">
-        <v>2254800</v>
+        <v>2268300</v>
       </c>
       <c r="F52" s="3">
-        <v>1558500</v>
+        <v>1567800</v>
       </c>
       <c r="G52" s="3">
-        <v>1415200</v>
+        <v>1423700</v>
       </c>
       <c r="H52" s="3">
-        <v>2123500</v>
+        <v>2136200</v>
       </c>
       <c r="I52" s="3">
-        <v>30029500</v>
+        <v>30209800</v>
       </c>
       <c r="J52" s="3">
-        <v>5760200</v>
+        <v>5794700</v>
       </c>
       <c r="K52" s="3">
         <v>403900</v>
@@ -1953,25 +1953,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>736690000</v>
+        <v>741113000</v>
       </c>
       <c r="E54" s="3">
-        <v>723421000</v>
+        <v>727764000</v>
       </c>
       <c r="F54" s="3">
-        <v>652212000</v>
+        <v>656128000</v>
       </c>
       <c r="G54" s="3">
-        <v>694475000</v>
+        <v>698644000</v>
       </c>
       <c r="H54" s="3">
-        <v>653732000</v>
+        <v>657656000</v>
       </c>
       <c r="I54" s="3">
-        <v>628442000</v>
+        <v>632215000</v>
       </c>
       <c r="J54" s="3">
-        <v>597888000</v>
+        <v>601478000</v>
       </c>
       <c r="K54" s="3">
         <v>593110000</v>
@@ -2011,25 +2011,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10059100</v>
+        <v>10119500</v>
       </c>
       <c r="E57" s="3">
-        <v>6553100</v>
+        <v>6592400</v>
       </c>
       <c r="F57" s="3">
-        <v>5761500</v>
+        <v>5796100</v>
       </c>
       <c r="G57" s="3">
-        <v>6082000</v>
+        <v>6118500</v>
       </c>
       <c r="H57" s="3">
-        <v>5309100</v>
+        <v>5341000</v>
       </c>
       <c r="I57" s="3">
-        <v>4593500</v>
+        <v>4621000</v>
       </c>
       <c r="J57" s="3">
-        <v>5563600</v>
+        <v>5597000</v>
       </c>
       <c r="K57" s="3">
         <v>1052200</v>
@@ -2071,25 +2071,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>203200</v>
+        <v>204400</v>
       </c>
       <c r="E59" s="3">
-        <v>552400</v>
+        <v>555700</v>
       </c>
       <c r="F59" s="3">
-        <v>279200</v>
+        <v>280900</v>
       </c>
       <c r="G59" s="3">
-        <v>232500</v>
+        <v>233900</v>
       </c>
       <c r="H59" s="3">
-        <v>173200</v>
+        <v>174300</v>
       </c>
       <c r="I59" s="3">
-        <v>199900</v>
+        <v>201100</v>
       </c>
       <c r="J59" s="3">
-        <v>160600</v>
+        <v>161500</v>
       </c>
       <c r="K59" s="3">
         <v>2063500</v>
@@ -2131,25 +2131,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>77300100</v>
+        <v>77764200</v>
       </c>
       <c r="E61" s="3">
-        <v>62455000</v>
+        <v>62829900</v>
       </c>
       <c r="F61" s="3">
-        <v>67332300</v>
+        <v>67736500</v>
       </c>
       <c r="G61" s="3">
-        <v>79734800</v>
+        <v>80213500</v>
       </c>
       <c r="H61" s="3">
-        <v>86413100</v>
+        <v>86931900</v>
       </c>
       <c r="I61" s="3">
-        <v>80741600</v>
+        <v>81226300</v>
       </c>
       <c r="J61" s="3">
-        <v>71942400</v>
+        <v>72374300</v>
       </c>
       <c r="K61" s="3">
         <v>74270500</v>
@@ -2161,25 +2161,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1577800</v>
+        <v>1587300</v>
       </c>
       <c r="E62" s="3">
-        <v>1668400</v>
+        <v>1678400</v>
       </c>
       <c r="F62" s="3">
-        <v>1922900</v>
+        <v>1934500</v>
       </c>
       <c r="G62" s="3">
-        <v>2168800</v>
+        <v>2181800</v>
       </c>
       <c r="H62" s="3">
-        <v>1918300</v>
+        <v>1929800</v>
       </c>
       <c r="I62" s="3">
-        <v>2691200</v>
+        <v>2707300</v>
       </c>
       <c r="J62" s="3">
-        <v>942800</v>
+        <v>948500</v>
       </c>
       <c r="K62" s="3">
         <v>964000</v>
@@ -2281,25 +2281,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>690385000</v>
+        <v>694530000</v>
       </c>
       <c r="E66" s="3">
-        <v>679507000</v>
+        <v>683587000</v>
       </c>
       <c r="F66" s="3">
-        <v>609792000</v>
+        <v>613453000</v>
       </c>
       <c r="G66" s="3">
-        <v>653640000</v>
+        <v>657564000</v>
       </c>
       <c r="H66" s="3">
-        <v>613232000</v>
+        <v>616913000</v>
       </c>
       <c r="I66" s="3">
-        <v>588954000</v>
+        <v>592490000</v>
       </c>
       <c r="J66" s="3">
-        <v>558604000</v>
+        <v>561957000</v>
       </c>
       <c r="K66" s="3">
         <v>555626000</v>
@@ -2445,25 +2445,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>28123900</v>
+        <v>28292700</v>
       </c>
       <c r="E72" s="3">
-        <v>26500100</v>
+        <v>26659200</v>
       </c>
       <c r="F72" s="3">
-        <v>24324600</v>
+        <v>24470600</v>
       </c>
       <c r="G72" s="3">
-        <v>22199800</v>
+        <v>22333100</v>
       </c>
       <c r="H72" s="3">
-        <v>21808700</v>
+        <v>21939600</v>
       </c>
       <c r="I72" s="3">
-        <v>21193700</v>
+        <v>21320900</v>
       </c>
       <c r="J72" s="3">
-        <v>19921000</v>
+        <v>20040600</v>
       </c>
       <c r="K72" s="3">
         <v>18172500</v>
@@ -2565,25 +2565,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46304500</v>
+        <v>46582500</v>
       </c>
       <c r="E76" s="3">
-        <v>43913800</v>
+        <v>44177500</v>
       </c>
       <c r="F76" s="3">
-        <v>42420000</v>
+        <v>42674600</v>
       </c>
       <c r="G76" s="3">
-        <v>40835500</v>
+        <v>41080700</v>
       </c>
       <c r="H76" s="3">
-        <v>40499700</v>
+        <v>40742800</v>
       </c>
       <c r="I76" s="3">
-        <v>39488300</v>
+        <v>39725300</v>
       </c>
       <c r="J76" s="3">
-        <v>39284400</v>
+        <v>39520200</v>
       </c>
       <c r="K76" s="3">
         <v>37483400</v>
@@ -2660,25 +2660,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4729400</v>
+        <v>4757800</v>
       </c>
       <c r="E81" s="3">
-        <v>4743400</v>
+        <v>4771900</v>
       </c>
       <c r="F81" s="3">
-        <v>4105700</v>
+        <v>4130400</v>
       </c>
       <c r="G81" s="3">
-        <v>2383400</v>
+        <v>2397700</v>
       </c>
       <c r="H81" s="3">
-        <v>3966500</v>
+        <v>3990300</v>
       </c>
       <c r="I81" s="3">
-        <v>4264300</v>
+        <v>4289900</v>
       </c>
       <c r="J81" s="3">
-        <v>4268300</v>
+        <v>4293900</v>
       </c>
       <c r="K81" s="3">
         <v>3701100</v>
@@ -2704,25 +2704,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>615000</v>
+        <v>618700</v>
       </c>
       <c r="E83" s="3">
-        <v>671600</v>
+        <v>675700</v>
       </c>
       <c r="F83" s="3">
-        <v>724300</v>
+        <v>728600</v>
       </c>
       <c r="G83" s="3">
-        <v>926800</v>
+        <v>932400</v>
       </c>
       <c r="H83" s="3">
-        <v>580300</v>
+        <v>583800</v>
       </c>
       <c r="I83" s="3">
-        <v>798900</v>
+        <v>803700</v>
       </c>
       <c r="J83" s="3">
-        <v>647600</v>
+        <v>651500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -2884,25 +2884,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4323000</v>
+        <v>4348900</v>
       </c>
       <c r="E89" s="3">
-        <v>13443300</v>
+        <v>13524000</v>
       </c>
       <c r="F89" s="3">
-        <v>29198600</v>
+        <v>29373900</v>
       </c>
       <c r="G89" s="3">
-        <v>26839900</v>
+        <v>27001000</v>
       </c>
       <c r="H89" s="3">
-        <v>-3031700</v>
+        <v>-3049900</v>
       </c>
       <c r="I89" s="3">
-        <v>7040100</v>
+        <v>7082400</v>
       </c>
       <c r="J89" s="3">
-        <v>16022500</v>
+        <v>16118700</v>
       </c>
       <c r="K89" s="3">
         <v>7028200</v>
@@ -3018,25 +3018,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7120100</v>
+        <v>-7162800</v>
       </c>
       <c r="E94" s="3">
-        <v>-1210700</v>
+        <v>-1217900</v>
       </c>
       <c r="F94" s="3">
-        <v>6834900</v>
+        <v>6875900</v>
       </c>
       <c r="G94" s="3">
-        <v>-7639100</v>
+        <v>-7685000</v>
       </c>
       <c r="H94" s="3">
-        <v>-137300</v>
+        <v>-138100</v>
       </c>
       <c r="I94" s="3">
-        <v>110600</v>
+        <v>111300</v>
       </c>
       <c r="J94" s="3">
-        <v>-8548600</v>
+        <v>-8599900</v>
       </c>
       <c r="K94" s="3">
         <v>-9342000</v>
@@ -3062,25 +3062,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2918400</v>
+        <v>-2935900</v>
       </c>
       <c r="E96" s="3">
-        <v>-2521300</v>
+        <v>-2536400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1888300</v>
+        <v>-1899600</v>
       </c>
       <c r="G96" s="3">
-        <v>-1906300</v>
+        <v>-1917700</v>
       </c>
       <c r="H96" s="3">
-        <v>-2979000</v>
+        <v>-2996900</v>
       </c>
       <c r="I96" s="3">
-        <v>-3040300</v>
+        <v>-3058600</v>
       </c>
       <c r="J96" s="3">
-        <v>-2922400</v>
+        <v>-2939900</v>
       </c>
       <c r="K96" s="3">
         <v>-2958800</v>
@@ -3182,25 +3182,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2921700</v>
+        <v>2939300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1562500</v>
+        <v>-1571900</v>
       </c>
       <c r="F100" s="3">
-        <v>-6444500</v>
+        <v>-6483100</v>
       </c>
       <c r="G100" s="3">
-        <v>-287800</v>
+        <v>-289600</v>
       </c>
       <c r="H100" s="3">
-        <v>-1839700</v>
+        <v>-1850700</v>
       </c>
       <c r="I100" s="3">
-        <v>1745700</v>
+        <v>1756200</v>
       </c>
       <c r="J100" s="3">
-        <v>-4492200</v>
+        <v>-4519200</v>
       </c>
       <c r="K100" s="3">
         <v>1269400</v>
@@ -3212,25 +3212,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-109900</v>
+        <v>-110600</v>
       </c>
       <c r="E101" s="3">
-        <v>571700</v>
+        <v>575100</v>
       </c>
       <c r="F101" s="3">
-        <v>-713600</v>
+        <v>-717900</v>
       </c>
       <c r="G101" s="3">
-        <v>-1387900</v>
+        <v>-1396200</v>
       </c>
       <c r="H101" s="3">
-        <v>2781100</v>
+        <v>2797800</v>
       </c>
       <c r="I101" s="3">
-        <v>2374700</v>
+        <v>2388900</v>
       </c>
       <c r="J101" s="3">
-        <v>-1763700</v>
+        <v>-1774300</v>
       </c>
       <c r="K101" s="3">
         <v>-938100</v>
@@ -3245,22 +3245,22 @@
         <v>14700</v>
       </c>
       <c r="E102" s="3">
-        <v>11241800</v>
+        <v>11309300</v>
       </c>
       <c r="F102" s="3">
-        <v>28875400</v>
+        <v>29048800</v>
       </c>
       <c r="G102" s="3">
-        <v>17525000</v>
+        <v>17630200</v>
       </c>
       <c r="H102" s="3">
-        <v>-2227400</v>
+        <v>-2240800</v>
       </c>
       <c r="I102" s="3">
-        <v>11271100</v>
+        <v>11338800</v>
       </c>
       <c r="J102" s="3">
-        <v>1218000</v>
+        <v>1225300</v>
       </c>
       <c r="K102" s="3">
         <v>-1982500</v>

--- a/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANZGY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>ANZGY</t>
   </si>
@@ -656,87 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44469</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44104</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43738</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43373</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43008</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42643</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>33449300</v>
+        <v>13964500</v>
       </c>
       <c r="E8" s="3">
-        <v>15825100</v>
+        <v>13051600</v>
       </c>
       <c r="F8" s="3">
-        <v>13090300</v>
+        <v>12664600</v>
       </c>
       <c r="G8" s="3">
-        <v>16372700</v>
+        <v>13028400</v>
       </c>
       <c r="H8" s="3">
-        <v>20830900</v>
+        <v>10680300</v>
       </c>
       <c r="I8" s="3">
-        <v>20328200</v>
+        <v>12133900</v>
       </c>
       <c r="J8" s="3">
+        <v>13967400</v>
+      </c>
+      <c r="K8" s="3">
         <v>19519100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19417200</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,39 +770,45 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>13964500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13051600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12664600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13028400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>10680300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>12133900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>13967400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,9 +851,12 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>162900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>109100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>65100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>142000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>311800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>51900</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-338500</v>
+        <v>417400</v>
       </c>
       <c r="E15" s="3">
-        <v>-387400</v>
+        <v>389100</v>
       </c>
       <c r="F15" s="3">
-        <v>-427700</v>
+        <v>407800</v>
       </c>
       <c r="G15" s="3">
-        <v>-575100</v>
+        <v>473000</v>
       </c>
       <c r="H15" s="3">
-        <v>-465200</v>
+        <v>526200</v>
       </c>
       <c r="I15" s="3">
-        <v>-663600</v>
+        <v>238800</v>
       </c>
       <c r="J15" s="3">
+        <v>273600</v>
+      </c>
+      <c r="K15" s="3">
         <v>-483300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-956200</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22499300</v>
+        <v>7284200</v>
       </c>
       <c r="E17" s="3">
-        <v>5699600</v>
+        <v>6433500</v>
       </c>
       <c r="F17" s="3">
-        <v>3218100</v>
+        <v>6106200</v>
       </c>
       <c r="G17" s="3">
-        <v>8791000</v>
+        <v>6413900</v>
       </c>
       <c r="H17" s="3">
-        <v>11751700</v>
+        <v>6414300</v>
       </c>
       <c r="I17" s="3">
-        <v>11060600</v>
+        <v>6066000</v>
       </c>
       <c r="J17" s="3">
+        <v>6458900</v>
+      </c>
+      <c r="K17" s="3">
         <v>10351400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10881700</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10950000</v>
+        <v>6680300</v>
       </c>
       <c r="E18" s="3">
-        <v>10125600</v>
+        <v>6618100</v>
       </c>
       <c r="F18" s="3">
-        <v>9872200</v>
+        <v>6558400</v>
       </c>
       <c r="G18" s="3">
-        <v>7581800</v>
+        <v>6614500</v>
       </c>
       <c r="H18" s="3">
-        <v>9079200</v>
+        <v>4265900</v>
       </c>
       <c r="I18" s="3">
-        <v>9267600</v>
+        <v>6068000</v>
       </c>
       <c r="J18" s="3">
+        <v>7508500</v>
+      </c>
+      <c r="K18" s="3">
         <v>9167700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8535500</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,158 +1046,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-4196700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-3369600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-3882400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-3884400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3100100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2634900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2978800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3233700</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7373700</v>
+        <v>7097700</v>
       </c>
       <c r="E21" s="3">
-        <v>7433500</v>
+        <v>7007200</v>
       </c>
       <c r="F21" s="3">
-        <v>6720500</v>
+        <v>6966200</v>
       </c>
       <c r="G21" s="3">
-        <v>4632400</v>
+        <v>7087500</v>
       </c>
       <c r="H21" s="3">
-        <v>6564600</v>
+        <v>4792100</v>
       </c>
       <c r="I21" s="3">
-        <v>7438600</v>
+        <v>6306700</v>
       </c>
       <c r="J21" s="3">
+        <v>7782100</v>
+      </c>
+      <c r="K21" s="3">
         <v>6842300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6753300</v>
+        <v>6517400</v>
       </c>
       <c r="E23" s="3">
-        <v>6756000</v>
+        <v>6509000</v>
       </c>
       <c r="F23" s="3">
-        <v>5989800</v>
+        <v>6493400</v>
       </c>
       <c r="G23" s="3">
-        <v>3697400</v>
+        <v>6472500</v>
       </c>
       <c r="H23" s="3">
-        <v>5979100</v>
+        <v>3954100</v>
       </c>
       <c r="I23" s="3">
-        <v>6632600</v>
+        <v>6016100</v>
       </c>
       <c r="J23" s="3">
+        <v>7162500</v>
+      </c>
+      <c r="K23" s="3">
         <v>6188900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5301800</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1976700</v>
+        <v>1962100</v>
       </c>
       <c r="E24" s="3">
-        <v>1970700</v>
+        <v>1905500</v>
       </c>
       <c r="F24" s="3">
-        <v>1847300</v>
+        <v>1894100</v>
       </c>
       <c r="G24" s="3">
-        <v>1233400</v>
+        <v>1996200</v>
       </c>
       <c r="H24" s="3">
-        <v>1748800</v>
+        <v>1319000</v>
       </c>
       <c r="I24" s="3">
-        <v>1866100</v>
+        <v>1759600</v>
       </c>
       <c r="J24" s="3">
+        <v>2015200</v>
+      </c>
+      <c r="K24" s="3">
         <v>1926400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1593500</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4776600</v>
+        <v>4555200</v>
       </c>
       <c r="E26" s="3">
-        <v>4785300</v>
+        <v>4603500</v>
       </c>
       <c r="F26" s="3">
-        <v>4142500</v>
+        <v>4599300</v>
       </c>
       <c r="G26" s="3">
-        <v>2464000</v>
+        <v>4476300</v>
       </c>
       <c r="H26" s="3">
-        <v>4230300</v>
+        <v>2635100</v>
       </c>
       <c r="I26" s="3">
-        <v>4766500</v>
+        <v>4256400</v>
       </c>
       <c r="J26" s="3">
+        <v>5147300</v>
+      </c>
+      <c r="K26" s="3">
         <v>4262400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3708300</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4757800</v>
+        <v>4531000</v>
       </c>
       <c r="E27" s="3">
-        <v>4784600</v>
+        <v>4585400</v>
       </c>
       <c r="F27" s="3">
-        <v>4141800</v>
+        <v>4586400</v>
       </c>
       <c r="G27" s="3">
-        <v>2463400</v>
+        <v>4463300</v>
       </c>
       <c r="H27" s="3">
-        <v>4220200</v>
+        <v>2564200</v>
       </c>
       <c r="I27" s="3">
-        <v>4755800</v>
+        <v>4015000</v>
       </c>
       <c r="J27" s="3">
+        <v>4632600</v>
+      </c>
+      <c r="K27" s="3">
         <v>4252400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3701100</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1293,29 +1353,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-12700</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-11400</v>
+        <v>-12200</v>
       </c>
       <c r="G29" s="3">
-        <v>-65700</v>
+        <v>-12300</v>
       </c>
       <c r="H29" s="3">
-        <v>-229900</v>
+        <v>-70300</v>
       </c>
       <c r="I29" s="3">
-        <v>-465900</v>
+        <v>-231300</v>
       </c>
       <c r="J29" s="3">
+        <v>-503100</v>
+      </c>
+      <c r="K29" s="3">
         <v>41600</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>4196700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3369600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3882400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>3884400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3100100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2634900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>2978800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3233700</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4757800</v>
+        <v>4531000</v>
       </c>
       <c r="E33" s="3">
-        <v>4771900</v>
+        <v>4585400</v>
       </c>
       <c r="F33" s="3">
-        <v>4130400</v>
+        <v>4586400</v>
       </c>
       <c r="G33" s="3">
-        <v>2397700</v>
+        <v>4463300</v>
       </c>
       <c r="H33" s="3">
-        <v>3990300</v>
+        <v>2564200</v>
       </c>
       <c r="I33" s="3">
-        <v>4289900</v>
+        <v>4015000</v>
       </c>
       <c r="J33" s="3">
+        <v>4632600</v>
+      </c>
+      <c r="K33" s="3">
         <v>4293900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3701100</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4757800</v>
+        <v>4531000</v>
       </c>
       <c r="E35" s="3">
-        <v>4771900</v>
+        <v>4585400</v>
       </c>
       <c r="F35" s="3">
-        <v>4130400</v>
+        <v>4586400</v>
       </c>
       <c r="G35" s="3">
-        <v>2397700</v>
+        <v>4463300</v>
       </c>
       <c r="H35" s="3">
-        <v>3990300</v>
+        <v>2564200</v>
       </c>
       <c r="I35" s="3">
-        <v>4289900</v>
+        <v>4015000</v>
       </c>
       <c r="J35" s="3">
+        <v>4632600</v>
+      </c>
+      <c r="K35" s="3">
         <v>4293900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3701100</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44469</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44104</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43738</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43373</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43008</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42643</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,278 +1642,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>214593000</v>
+        <v>74077500</v>
       </c>
       <c r="E41" s="3">
-        <v>109122000</v>
+        <v>88044800</v>
       </c>
       <c r="F41" s="3">
-        <v>98701700</v>
+        <v>98013100</v>
       </c>
       <c r="G41" s="3">
-        <v>57562700</v>
+        <v>96834000</v>
       </c>
       <c r="H41" s="3">
-        <v>45731900</v>
+        <v>51842300</v>
       </c>
       <c r="I41" s="3">
-        <v>101321000</v>
+        <v>38000900</v>
       </c>
       <c r="J41" s="3">
+        <v>40777400</v>
+      </c>
+      <c r="K41" s="3">
         <v>41106100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38753400</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>92286200</v>
+        <v>100013900</v>
       </c>
       <c r="E42" s="3">
-        <v>103298000</v>
+        <v>83320000</v>
       </c>
       <c r="F42" s="3">
-        <v>73840900</v>
+        <v>91101000</v>
       </c>
       <c r="G42" s="3">
-        <v>158295000</v>
+        <v>73153000</v>
       </c>
       <c r="H42" s="3">
-        <v>136823000</v>
+        <v>159030100</v>
       </c>
       <c r="I42" s="3">
-        <v>97571500</v>
+        <v>127546400</v>
       </c>
       <c r="J42" s="3">
+        <v>97319600</v>
+      </c>
+      <c r="K42" s="3">
         <v>91628000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>109372000</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>73600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>41300</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>115400</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>178700</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>10798000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>11555100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>11249800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>12093300</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>15662400</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>13877400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>42424900</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>185382400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>183410300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>200800800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>182607600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>227224400</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>180196300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>181354300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1574500</v>
+        <v>98449000</v>
       </c>
       <c r="E47" s="3">
-        <v>1461900</v>
+        <v>64385400</v>
       </c>
       <c r="F47" s="3">
-        <v>1321800</v>
+        <v>56908900</v>
       </c>
       <c r="G47" s="3">
-        <v>1450500</v>
+        <v>61638400</v>
       </c>
       <c r="H47" s="3">
-        <v>1982100</v>
+        <v>68498200</v>
       </c>
       <c r="I47" s="3">
-        <v>1711300</v>
+        <v>58451500</v>
       </c>
       <c r="J47" s="3">
+        <v>55618500</v>
+      </c>
+      <c r="K47" s="3">
         <v>1506800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2769500</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1376100</v>
+        <v>1540600</v>
       </c>
       <c r="E48" s="3">
-        <v>1629500</v>
+        <v>1324800</v>
       </c>
       <c r="F48" s="3">
-        <v>1832600</v>
+        <v>1566200</v>
       </c>
       <c r="G48" s="3">
-        <v>2019600</v>
+        <v>1980300</v>
       </c>
       <c r="H48" s="3">
-        <v>1289700</v>
+        <v>2159900</v>
       </c>
       <c r="I48" s="3">
-        <v>1228700</v>
+        <v>1297600</v>
       </c>
       <c r="J48" s="3">
+        <v>1326800</v>
+      </c>
+      <c r="K48" s="3">
         <v>1317100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1429500</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5440200</v>
+        <v>3821000</v>
       </c>
       <c r="E49" s="3">
-        <v>2598800</v>
+        <v>2618600</v>
       </c>
       <c r="F49" s="3">
-        <v>2764300</v>
+        <v>2497700</v>
       </c>
       <c r="G49" s="3">
-        <v>2935200</v>
+        <v>2987100</v>
       </c>
       <c r="H49" s="3">
-        <v>3258300</v>
+        <v>3139100</v>
       </c>
       <c r="I49" s="3">
-        <v>6609200</v>
+        <v>3278500</v>
       </c>
       <c r="J49" s="3">
+        <v>3568600</v>
+      </c>
+      <c r="K49" s="3">
         <v>4672000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4973800</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2244200</v>
+        <v>3727400</v>
       </c>
       <c r="E52" s="3">
-        <v>2268300</v>
+        <v>3311000</v>
       </c>
       <c r="F52" s="3">
-        <v>1567800</v>
+        <v>2327700</v>
       </c>
       <c r="G52" s="3">
-        <v>1423700</v>
+        <v>1981000</v>
       </c>
       <c r="H52" s="3">
-        <v>2136200</v>
+        <v>2253800</v>
       </c>
       <c r="I52" s="3">
-        <v>30209800</v>
+        <v>2627000</v>
       </c>
       <c r="J52" s="3">
+        <v>2661600</v>
+      </c>
+      <c r="K52" s="3">
         <v>5794700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>403900</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>741113000</v>
+        <v>852190900</v>
       </c>
       <c r="E54" s="3">
-        <v>727764000</v>
+        <v>713456200</v>
       </c>
       <c r="F54" s="3">
-        <v>656128000</v>
+        <v>699477500</v>
       </c>
       <c r="G54" s="3">
-        <v>698644000</v>
+        <v>709008400</v>
       </c>
       <c r="H54" s="3">
-        <v>657656000</v>
+        <v>747158400</v>
       </c>
       <c r="I54" s="3">
-        <v>632215000</v>
+        <v>661723200</v>
       </c>
       <c r="J54" s="3">
+        <v>682723100</v>
+      </c>
+      <c r="K54" s="3">
         <v>601478000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>593110000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,188 +2134,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10119500</v>
+        <v>593473600</v>
       </c>
       <c r="E57" s="3">
-        <v>6592400</v>
+        <v>504355700</v>
       </c>
       <c r="F57" s="3">
-        <v>5796100</v>
+        <v>488377100</v>
       </c>
       <c r="G57" s="3">
-        <v>6118500</v>
+        <v>519608900</v>
       </c>
       <c r="H57" s="3">
-        <v>5341000</v>
+        <v>482574200</v>
       </c>
       <c r="I57" s="3">
-        <v>4621000</v>
+        <v>422111700</v>
       </c>
       <c r="J57" s="3">
+        <v>447448400</v>
+      </c>
+      <c r="K57" s="3">
         <v>5597000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1052200</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>95871900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>72685700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>96553300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>61313900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>121764200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>103571900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>66059400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>204400</v>
+        <v>20213500</v>
       </c>
       <c r="E59" s="3">
-        <v>555700</v>
+        <v>22727600</v>
       </c>
       <c r="F59" s="3">
-        <v>280900</v>
+        <v>19858900</v>
       </c>
       <c r="G59" s="3">
-        <v>233900</v>
+        <v>17023800</v>
       </c>
       <c r="H59" s="3">
-        <v>174300</v>
+        <v>22863100</v>
       </c>
       <c r="I59" s="3">
-        <v>201100</v>
+        <v>14282700</v>
       </c>
       <c r="J59" s="3">
+        <v>47637400</v>
+      </c>
+      <c r="K59" s="3">
         <v>161500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2063500</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>710983800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>600716900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>605639700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>597946500</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>627201400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>539966300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>561145100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>77764200</v>
+        <v>84632200</v>
       </c>
       <c r="E61" s="3">
-        <v>62829900</v>
+        <v>61248600</v>
       </c>
       <c r="F61" s="3">
-        <v>67736500</v>
+        <v>44630200</v>
       </c>
       <c r="G61" s="3">
-        <v>80213500</v>
+        <v>57575700</v>
       </c>
       <c r="H61" s="3">
-        <v>86931900</v>
+        <v>68228700</v>
       </c>
       <c r="I61" s="3">
-        <v>81226300</v>
+        <v>73439000</v>
       </c>
       <c r="J61" s="3">
+        <v>72091200</v>
+      </c>
+      <c r="K61" s="3">
         <v>72374300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>74270500</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1587300</v>
+        <v>7551800</v>
       </c>
       <c r="E62" s="3">
-        <v>1678400</v>
+        <v>6256700</v>
       </c>
       <c r="F62" s="3">
-        <v>1934500</v>
+        <v>6375500</v>
       </c>
       <c r="G62" s="3">
-        <v>2181800</v>
+        <v>7305500</v>
       </c>
       <c r="H62" s="3">
-        <v>1929800</v>
+        <v>7688200</v>
       </c>
       <c r="I62" s="3">
-        <v>2707300</v>
+        <v>7234100</v>
       </c>
       <c r="J62" s="3">
+        <v>6421300</v>
+      </c>
+      <c r="K62" s="3">
         <v>948500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>964000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>694530000</v>
+        <v>803221900</v>
       </c>
       <c r="E66" s="3">
-        <v>683587000</v>
+        <v>668275200</v>
       </c>
       <c r="F66" s="3">
-        <v>613453000</v>
+        <v>656698900</v>
       </c>
       <c r="G66" s="3">
-        <v>657564000</v>
+        <v>662886400</v>
       </c>
       <c r="H66" s="3">
-        <v>616913000</v>
+        <v>703217900</v>
       </c>
       <c r="I66" s="3">
-        <v>592490000</v>
+        <v>620721000</v>
       </c>
       <c r="J66" s="3">
+        <v>639722800</v>
+      </c>
+      <c r="K66" s="3">
         <v>561957000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>555626000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>28292700</v>
+        <v>30124800</v>
       </c>
       <c r="E72" s="3">
-        <v>26659200</v>
+        <v>27197500</v>
       </c>
       <c r="F72" s="3">
-        <v>24470600</v>
+        <v>25586900</v>
       </c>
       <c r="G72" s="3">
-        <v>22333100</v>
+        <v>26403700</v>
       </c>
       <c r="H72" s="3">
-        <v>21939600</v>
+        <v>23838700</v>
       </c>
       <c r="I72" s="3">
-        <v>21320900</v>
+        <v>22030100</v>
       </c>
       <c r="J72" s="3">
+        <v>22972900</v>
+      </c>
+      <c r="K72" s="3">
         <v>20040600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18172500</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46582500</v>
+        <v>48434400</v>
       </c>
       <c r="E76" s="3">
-        <v>44177500</v>
+        <v>44844200</v>
       </c>
       <c r="F76" s="3">
-        <v>42674600</v>
+        <v>42460400</v>
       </c>
       <c r="G76" s="3">
-        <v>41080700</v>
+        <v>46114000</v>
       </c>
       <c r="H76" s="3">
-        <v>40742800</v>
+        <v>43933300</v>
       </c>
       <c r="I76" s="3">
-        <v>39725300</v>
+        <v>40994800</v>
       </c>
       <c r="J76" s="3">
+        <v>42899000</v>
+      </c>
+      <c r="K76" s="3">
         <v>39520200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37483400</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44469</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43738</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43373</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43008</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42643</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4757800</v>
+        <v>4531000</v>
       </c>
       <c r="E81" s="3">
-        <v>4771900</v>
+        <v>4585400</v>
       </c>
       <c r="F81" s="3">
-        <v>4130400</v>
+        <v>4586400</v>
       </c>
       <c r="G81" s="3">
-        <v>2397700</v>
+        <v>4463300</v>
       </c>
       <c r="H81" s="3">
-        <v>3990300</v>
+        <v>2564200</v>
       </c>
       <c r="I81" s="3">
-        <v>4289900</v>
+        <v>4015000</v>
       </c>
       <c r="J81" s="3">
+        <v>4632600</v>
+      </c>
+      <c r="K81" s="3">
         <v>4293900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3701100</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>618700</v>
+        <v>413200</v>
       </c>
       <c r="E83" s="3">
-        <v>675700</v>
+        <v>385200</v>
       </c>
       <c r="F83" s="3">
-        <v>728600</v>
+        <v>405200</v>
       </c>
       <c r="G83" s="3">
-        <v>932400</v>
+        <v>471500</v>
       </c>
       <c r="H83" s="3">
-        <v>583800</v>
+        <v>525400</v>
       </c>
       <c r="I83" s="3">
-        <v>803700</v>
+        <v>238800</v>
       </c>
       <c r="J83" s="3">
+        <v>246100</v>
+      </c>
+      <c r="K83" s="3">
         <v>651500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4348900</v>
+        <v>-22181900</v>
       </c>
       <c r="E89" s="3">
-        <v>13524000</v>
+        <v>-9752200</v>
       </c>
       <c r="F89" s="3">
-        <v>29373900</v>
+        <v>-18491800</v>
       </c>
       <c r="G89" s="3">
-        <v>27001000</v>
+        <v>-3675200</v>
       </c>
       <c r="H89" s="3">
-        <v>-3049900</v>
+        <v>293200</v>
       </c>
       <c r="I89" s="3">
-        <v>7082400</v>
+        <v>-7793900</v>
       </c>
       <c r="J89" s="3">
+        <v>-1187800</v>
+      </c>
+      <c r="K89" s="3">
         <v>16118700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7028200</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-218500</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7162800</v>
+        <v>-29204000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1217900</v>
+        <v>-6895500</v>
       </c>
       <c r="F94" s="3">
-        <v>6875900</v>
+        <v>-1170600</v>
       </c>
       <c r="G94" s="3">
-        <v>-7685000</v>
+        <v>7430100</v>
       </c>
       <c r="H94" s="3">
-        <v>-138100</v>
+        <v>-8218600</v>
       </c>
       <c r="I94" s="3">
-        <v>111300</v>
+        <v>-138900</v>
       </c>
       <c r="J94" s="3">
+        <v>120200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8599900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9342000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2935900</v>
+        <v>3619200</v>
       </c>
       <c r="E96" s="3">
-        <v>-2536400</v>
+        <v>2826400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1899600</v>
+        <v>2437800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1917700</v>
+        <v>2052700</v>
       </c>
       <c r="H96" s="3">
-        <v>-2996900</v>
+        <v>2050900</v>
       </c>
       <c r="I96" s="3">
-        <v>-3058600</v>
+        <v>3015400</v>
       </c>
       <c r="J96" s="3">
+        <v>3302900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2939900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2958800</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2939300</v>
+        <v>41496200</v>
       </c>
       <c r="E100" s="3">
-        <v>-1571900</v>
+        <v>16768400</v>
       </c>
       <c r="F100" s="3">
-        <v>-6483100</v>
+        <v>29979400</v>
       </c>
       <c r="G100" s="3">
-        <v>-289600</v>
+        <v>28410800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1850700</v>
+        <v>28273100</v>
       </c>
       <c r="I100" s="3">
-        <v>1756200</v>
+        <v>2863000</v>
       </c>
       <c r="J100" s="3">
+        <v>10732500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4519200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1269400</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-110600</v>
+        <v>-2026600</v>
       </c>
       <c r="E101" s="3">
-        <v>575100</v>
+        <v>-106500</v>
       </c>
       <c r="F101" s="3">
-        <v>-717900</v>
+        <v>552800</v>
       </c>
       <c r="G101" s="3">
-        <v>-1396200</v>
+        <v>-775700</v>
       </c>
       <c r="H101" s="3">
-        <v>2797800</v>
+        <v>-1493200</v>
       </c>
       <c r="I101" s="3">
-        <v>2388900</v>
+        <v>2815100</v>
       </c>
       <c r="J101" s="3">
+        <v>2579800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1774300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-938100</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14700</v>
+        <v>-11916400</v>
       </c>
       <c r="E102" s="3">
-        <v>11309300</v>
+        <v>14200</v>
       </c>
       <c r="F102" s="3">
-        <v>29048800</v>
+        <v>10869700</v>
       </c>
       <c r="G102" s="3">
-        <v>17630200</v>
+        <v>31390000</v>
       </c>
       <c r="H102" s="3">
-        <v>-2240800</v>
+        <v>18854500</v>
       </c>
       <c r="I102" s="3">
-        <v>11338800</v>
+        <v>-2254700</v>
       </c>
       <c r="J102" s="3">
+        <v>12244700</v>
+      </c>
+      <c r="K102" s="3">
         <v>1225300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1982500</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
